--- a/1_Kanto_Data.xlsx
+++ b/1_Kanto_Data.xlsx
@@ -615,8 +615,8 @@
       <c r="H5" s="1">
         <v>0.35</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
+      <c r="I5" s="1">
+        <v>0.25</v>
       </c>
       <c r="J5" t="str">
         <v>Legacy</v>
@@ -662,8 +662,8 @@
       <c r="H6" s="1">
         <v>0.35</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="I6" s="1">
+        <v>0.25</v>
       </c>
       <c r="J6" t="str">
         <v>Legacy</v>
@@ -709,8 +709,8 @@
       <c r="H7" s="1">
         <v>0.15</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
+      <c r="I7" s="1">
+        <v>0.25</v>
       </c>
       <c r="J7" t="str">
         <v>Yes</v>
@@ -756,8 +756,8 @@
       <c r="H8" s="1">
         <v>0.15</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
+      <c r="I8" s="1">
+        <v>0.25</v>
       </c>
       <c r="J8" t="str">
         <v>Yes</v>
@@ -798,13 +798,13 @@
         <v>3-6</v>
       </c>
       <c r="G9" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H9" s="1">
         <v>0.36</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
+      <c r="I9" s="1">
+        <v>0.2</v>
       </c>
       <c r="J9" t="str">
         <v>Legacy</v>
@@ -845,13 +845,13 @@
         <v>3-6</v>
       </c>
       <c r="G10" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H10" s="1">
         <v>0.36</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
+      <c r="I10" s="1">
+        <v>0.2</v>
       </c>
       <c r="J10" t="str">
         <v>Legacy</v>
@@ -892,13 +892,13 @@
         <v>4-6</v>
       </c>
       <c r="G11" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H11" s="1">
         <v>0.1</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
+      <c r="I11" s="1">
+        <v>0.2</v>
       </c>
       <c r="J11" t="str">
         <v>Legacy</v>
@@ -939,13 +939,13 @@
         <v>4-6</v>
       </c>
       <c r="G12" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H12" s="1">
         <v>0.1</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
+      <c r="I12" s="1">
+        <v>0.2</v>
       </c>
       <c r="J12" t="str">
         <v>Legacy</v>
@@ -986,13 +986,13 @@
         <v>3-5</v>
       </c>
       <c r="G13" t="str">
-        <v>3-5</v>
+        <v>2-4</v>
       </c>
       <c r="H13" s="1">
         <v>0.08</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
+      <c r="I13" s="1">
+        <v>0.2</v>
       </c>
       <c r="J13" t="str">
         <v>Legacy</v>
@@ -1033,13 +1033,13 @@
         <v>6-9</v>
       </c>
       <c r="G14" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H14" s="1">
         <v>0.25</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
+      <c r="I14" s="1">
+        <v>0.125</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1080,13 +1080,13 @@
         <v>6-9</v>
       </c>
       <c r="G15" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H15" s="1">
         <v>0.25</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
+      <c r="I15" s="1">
+        <v>0.125</v>
       </c>
       <c r="J15" t="str">
         <v>Legacy</v>
@@ -1127,7 +1127,7 @@
         <v>6-9</v>
       </c>
       <c r="G16" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H16" s="1">
         <v>0.15</v>
@@ -1174,7 +1174,7 @@
         <v>6-9</v>
       </c>
       <c r="G17" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H17" s="1">
         <v>0.15</v>
@@ -1221,7 +1221,7 @@
         <v>5-7</v>
       </c>
       <c r="G18" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H18" s="1">
         <v>0.1</v>
@@ -1268,13 +1268,13 @@
         <v>8-10</v>
       </c>
       <c r="G19" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H19" s="1">
         <v>0.02</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
+      <c r="I19" s="1">
+        <v>0.125</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -1315,7 +1315,7 @@
         <v>6-8</v>
       </c>
       <c r="G20" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H20" s="1">
         <v>0.04</v>
@@ -1362,7 +1362,7 @@
         <v>6-8</v>
       </c>
       <c r="G21" t="str">
-        <v>5-7</v>
+        <v>4-6</v>
       </c>
       <c r="H21" s="1">
         <v>0.04</v>
@@ -1409,13 +1409,13 @@
         <v>8-13</v>
       </c>
       <c r="G22" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H22" s="1">
         <v>0.5</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
+      <c r="I22" s="1">
+        <v>0.2</v>
       </c>
       <c r="J22" t="str">
         <v>Yes</v>
@@ -1456,7 +1456,7 @@
         <v>8-12</v>
       </c>
       <c r="G23" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H23" s="1">
         <v>0.25</v>
@@ -1503,7 +1503,7 @@
         <v>8-12</v>
       </c>
       <c r="G24" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H24" s="1">
         <v>0.15</v>
@@ -1550,13 +1550,13 @@
         <v>9-13</v>
       </c>
       <c r="G25" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H25" s="1">
         <v>0.08</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
+      <c r="I25" s="1">
+        <v>0.2</v>
       </c>
       <c r="J25" t="str">
         <v>Yes</v>
@@ -1597,13 +1597,13 @@
         <v>11-14</v>
       </c>
       <c r="G26" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H26" s="1">
         <v>0.02</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
+      <c r="I26" s="1">
+        <v>0.2</v>
       </c>
       <c r="J26" t="str">
         <v>Yes</v>
@@ -1644,13 +1644,13 @@
         <v>11-15</v>
       </c>
       <c r="G27" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H27" s="1">
         <v>0.3</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
+      <c r="I27" s="1">
+        <v>0.2</v>
       </c>
       <c r="J27" t="str">
         <v>Yes</v>
@@ -1691,13 +1691,13 @@
         <v>11-15</v>
       </c>
       <c r="G28" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H28" s="1">
         <v>0.3</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
+      <c r="I28" s="1">
+        <v>0.2</v>
       </c>
       <c r="J28" t="str">
         <v>Yes</v>
@@ -1738,7 +1738,7 @@
         <v>11-15</v>
       </c>
       <c r="G29" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H29" s="1">
         <v>0.15</v>
@@ -1785,7 +1785,7 @@
         <v>10-14</v>
       </c>
       <c r="G30" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H30" s="1">
         <v>0.15</v>
@@ -1832,13 +1832,13 @@
         <v>10-14</v>
       </c>
       <c r="G31" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H31" s="1">
         <v>0.1</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="I31" s="1">
+        <v>0.2</v>
       </c>
       <c r="J31" t="str">
         <v>Legacy</v>
@@ -1879,7 +1879,7 @@
         <v>14-18</v>
       </c>
       <c r="G32" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H32" s="1">
         <v>0.25</v>
@@ -1926,7 +1926,7 @@
         <v>14-18</v>
       </c>
       <c r="G33" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H33" s="1">
         <v>0.25</v>
@@ -1973,7 +1973,7 @@
         <v>12-16</v>
       </c>
       <c r="G34" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H34" s="1">
         <v>0.2</v>
@@ -2020,7 +2020,7 @@
         <v>13-17</v>
       </c>
       <c r="G35" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H35" s="1">
         <v>0.15</v>
@@ -2067,7 +2067,7 @@
         <v>14-17</v>
       </c>
       <c r="G36" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H36" s="1">
         <v>0.15</v>
@@ -2114,7 +2114,7 @@
         <v>15-19</v>
       </c>
       <c r="G37" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H37" s="1">
         <v>0.25</v>
@@ -2161,7 +2161,7 @@
         <v>15-19</v>
       </c>
       <c r="G38" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H38" s="1">
         <v>0.25</v>
@@ -2208,7 +2208,7 @@
         <v>13-17</v>
       </c>
       <c r="G39" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H39" s="1">
         <v>0.2</v>
@@ -2255,7 +2255,7 @@
         <v>14-18</v>
       </c>
       <c r="G40" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H40" s="1">
         <v>0.15</v>
@@ -2302,7 +2302,7 @@
         <v>15-18</v>
       </c>
       <c r="G41" t="str">
-        <v>14-17</v>
+        <v>13-16</v>
       </c>
       <c r="H41" s="1">
         <v>0.15</v>
@@ -2349,13 +2349,13 @@
         <v>18-22</v>
       </c>
       <c r="G42" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H42" s="1">
         <v>0.4</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
+      <c r="I42" s="1">
+        <v>0.25</v>
       </c>
       <c r="J42" t="str">
         <v>Yes</v>
@@ -2396,13 +2396,13 @@
         <v>17-21</v>
       </c>
       <c r="G43" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H43" s="1">
         <v>0.35</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
+      <c r="I43" s="1">
+        <v>0.25</v>
       </c>
       <c r="J43" t="str">
         <v>Legacy</v>
@@ -2443,13 +2443,13 @@
         <v>18-22</v>
       </c>
       <c r="G44" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H44" s="1">
         <v>0.15</v>
       </c>
-      <c r="I44" t="str">
-        <v/>
+      <c r="I44" s="1">
+        <v>0.25</v>
       </c>
       <c r="J44" t="str">
         <v>Legacy</v>
@@ -2490,13 +2490,13 @@
         <v>18-22</v>
       </c>
       <c r="G45" t="str">
-        <v>16-19</v>
+        <v>15-18</v>
       </c>
       <c r="H45" s="1">
         <v>0.1</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="I45" s="1">
+        <v>0.25</v>
       </c>
       <c r="J45" t="str">
         <v>Legacy</v>
@@ -2537,13 +2537,13 @@
         <v>19-24</v>
       </c>
       <c r="G46" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H46" s="1">
         <v>0.3</v>
       </c>
-      <c r="I46" t="str">
-        <v/>
+      <c r="I46" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J46" t="str">
         <v>Yes</v>
@@ -2584,13 +2584,13 @@
         <v>18-23</v>
       </c>
       <c r="G47" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H47" s="1">
         <v>0.3</v>
       </c>
-      <c r="I47" t="str">
-        <v/>
+      <c r="I47" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J47" t="str">
         <v>Yes</v>
@@ -2631,7 +2631,7 @@
         <v>18-23</v>
       </c>
       <c r="G48" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H48" s="1">
         <v>0.15</v>
@@ -2678,7 +2678,7 @@
         <v>18-23</v>
       </c>
       <c r="G49" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H49" s="1">
         <v>0.15</v>
@@ -2725,13 +2725,13 @@
         <v>19-24</v>
       </c>
       <c r="G50" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H50" s="1">
         <v>0.05</v>
       </c>
-      <c r="I50" t="str">
-        <v/>
+      <c r="I50" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J50" t="str">
         <v>Yes</v>
@@ -2772,13 +2772,13 @@
         <v>19-24</v>
       </c>
       <c r="G51" t="str">
-        <v>18-21</v>
+        <v>17-20</v>
       </c>
       <c r="H51" s="1">
         <v>0.05</v>
       </c>
-      <c r="I51" t="str">
-        <v/>
+      <c r="I51" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J51" t="str">
         <v>Legacy</v>
@@ -2824,8 +2824,8 @@
       <c r="H52" s="1">
         <v>0.4</v>
       </c>
-      <c r="I52" t="str">
-        <v/>
+      <c r="I52" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J52" t="str">
         <v>Legacy</v>
@@ -2965,8 +2965,8 @@
       <c r="H55" s="1">
         <v>0.05</v>
       </c>
-      <c r="I55" t="str">
-        <v/>
+      <c r="I55" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J55" t="str">
         <v>Legacy</v>
@@ -3101,13 +3101,13 @@
         <v>23-29</v>
       </c>
       <c r="G58" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H58" s="1">
         <v>0.9</v>
       </c>
-      <c r="I58" t="str">
-        <v/>
+      <c r="I58" s="1">
+        <v>0.5</v>
       </c>
       <c r="J58" t="str">
         <v>Yes</v>
@@ -3148,13 +3148,13 @@
         <v>29-33</v>
       </c>
       <c r="G59" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H59" s="1">
         <v>0.1</v>
       </c>
-      <c r="I59" t="str">
-        <v/>
+      <c r="I59" s="1">
+        <v>0.5</v>
       </c>
       <c r="J59" t="str">
         <v>Yes</v>
@@ -3195,13 +3195,13 @@
         <v>25-30</v>
       </c>
       <c r="G60" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H60" s="1">
         <v>0.3</v>
       </c>
-      <c r="I60" t="str">
-        <v/>
+      <c r="I60" s="1">
+        <v>0.2</v>
       </c>
       <c r="J60" t="str">
         <v>Yes</v>
@@ -3242,13 +3242,13 @@
         <v>25-30</v>
       </c>
       <c r="G61" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H61" s="1">
         <v>0.3</v>
       </c>
-      <c r="I61" t="str">
-        <v/>
+      <c r="I61" s="1">
+        <v>0.2</v>
       </c>
       <c r="J61" t="str">
         <v>Yes</v>
@@ -3289,7 +3289,7 @@
         <v>26-31</v>
       </c>
       <c r="G62" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H62" s="1">
         <v>0.15</v>
@@ -3336,7 +3336,7 @@
         <v>24-29</v>
       </c>
       <c r="G63" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H63" s="1">
         <v>0.15</v>
@@ -3383,7 +3383,7 @@
         <v>24-29</v>
       </c>
       <c r="G64" t="str">
-        <v>25-28</v>
+        <v>24-27</v>
       </c>
       <c r="H64" s="1">
         <v>0.15</v>
@@ -3430,13 +3430,13 @@
         <v>27-32</v>
       </c>
       <c r="G65" t="str">
-        <v>27-30</v>
+        <v>26-29</v>
       </c>
       <c r="H65" s="1">
         <v>0.35</v>
       </c>
-      <c r="I65" t="str">
-        <v/>
+      <c r="I65" s="1">
+        <v>0.2</v>
       </c>
       <c r="J65" t="str">
         <v>Yes</v>
@@ -3477,13 +3477,13 @@
         <v>26-31</v>
       </c>
       <c r="G66" t="str">
-        <v>27-30</v>
+        <v>26-29</v>
       </c>
       <c r="H66" s="1">
         <v>0.3</v>
       </c>
-      <c r="I66" t="str">
-        <v/>
+      <c r="I66" s="1">
+        <v>0.2</v>
       </c>
       <c r="J66" t="str">
         <v>Legacy</v>
@@ -3524,7 +3524,7 @@
         <v>26-31</v>
       </c>
       <c r="G67" t="str">
-        <v>27-30</v>
+        <v>26-29</v>
       </c>
       <c r="H67" s="1">
         <v>0.25</v>
@@ -3571,13 +3571,13 @@
         <v>26-30</v>
       </c>
       <c r="G68" t="str">
-        <v>27-30</v>
+        <v>26-29</v>
       </c>
       <c r="H68" s="1">
         <v>0.05</v>
       </c>
-      <c r="I68" t="str">
-        <v/>
+      <c r="I68" s="1">
+        <v>0.2</v>
       </c>
       <c r="J68" t="str">
         <v>Yes</v>
@@ -3618,13 +3618,13 @@
         <v>26-30</v>
       </c>
       <c r="G69" t="str">
-        <v>27-30</v>
+        <v>26-29</v>
       </c>
       <c r="H69" s="1">
         <v>0.05</v>
       </c>
-      <c r="I69" t="str">
-        <v/>
+      <c r="I69" s="1">
+        <v>0.2</v>
       </c>
       <c r="J69" t="str">
         <v>Yes</v>
@@ -3670,8 +3670,8 @@
       <c r="H70" s="1">
         <v>0.4</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
+      <c r="I70" s="1">
+        <v>0.25</v>
       </c>
       <c r="J70" t="str">
         <v>Legacy</v>
@@ -3811,8 +3811,8 @@
       <c r="H73" s="1">
         <v>0.15</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
+      <c r="I73" s="1">
+        <v>0.25</v>
       </c>
       <c r="J73" t="str">
         <v>Legacy</v>
@@ -3853,7 +3853,7 @@
         <v>32-37</v>
       </c>
       <c r="G74" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H74" s="1">
         <v>0.25</v>
@@ -3900,7 +3900,7 @@
         <v>32-37</v>
       </c>
       <c r="G75" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H75" s="1">
         <v>0.25</v>
@@ -3947,7 +3947,7 @@
         <v>32-37</v>
       </c>
       <c r="G76" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H76" s="1">
         <v>0.2</v>
@@ -3994,7 +3994,7 @@
         <v>31-36</v>
       </c>
       <c r="G77" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H77" s="1">
         <v>0.2</v>
@@ -4041,13 +4041,13 @@
         <v>33-38</v>
       </c>
       <c r="G78" t="str">
-        <v>32-36</v>
+        <v>31-34</v>
       </c>
       <c r="H78" s="1">
         <v>0.1</v>
       </c>
-      <c r="I78" t="str">
-        <v/>
+      <c r="I78" s="1">
+        <v>0.2</v>
       </c>
       <c r="J78" t="str">
         <v>Legacy</v>
@@ -4088,13 +4088,13 @@
         <v>34-39</v>
       </c>
       <c r="G79" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H79" s="1">
         <v>0.3</v>
       </c>
-      <c r="I79" t="str">
-        <v/>
+      <c r="I79" s="1">
+        <v>0.2</v>
       </c>
       <c r="J79" t="str">
         <v>Yes</v>
@@ -4135,7 +4135,7 @@
         <v>33-38</v>
       </c>
       <c r="G80" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H80" s="1">
         <v>0.25</v>
@@ -4182,7 +4182,7 @@
         <v>34-39</v>
       </c>
       <c r="G81" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H81" s="1">
         <v>0.175</v>
@@ -4229,7 +4229,7 @@
         <v>34-39</v>
       </c>
       <c r="G82" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H82" s="1">
         <v>0.175</v>
@@ -4276,13 +4276,13 @@
         <v>35-40</v>
       </c>
       <c r="G83" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H83" s="1">
         <v>0.1</v>
       </c>
-      <c r="I83" t="str">
-        <v/>
+      <c r="I83" s="1">
+        <v>0.2</v>
       </c>
       <c r="J83" t="str">
         <v>Legacy</v>
@@ -4323,7 +4323,7 @@
         <v>35-42</v>
       </c>
       <c r="G84" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H84" s="1">
         <v>0.333</v>
@@ -4370,7 +4370,7 @@
         <v>35-42</v>
       </c>
       <c r="G85" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H85" s="1">
         <v>0.333</v>
@@ -4417,7 +4417,7 @@
         <v>35-42</v>
       </c>
       <c r="G86" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H86" s="1">
         <v>0.334</v>
@@ -4464,7 +4464,7 @@
         <v>41-48</v>
       </c>
       <c r="G87" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H87" s="1">
         <v>0.333</v>
@@ -4511,7 +4511,7 @@
         <v>41-48</v>
       </c>
       <c r="G88" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H88" s="1">
         <v>0.333</v>
@@ -4558,7 +4558,7 @@
         <v>41-48</v>
       </c>
       <c r="G89" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H89" s="1">
         <v>0.334</v>
@@ -4605,7 +4605,7 @@
         <v>59-66</v>
       </c>
       <c r="G90" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H90" s="1">
         <v>0.333</v>
@@ -4652,7 +4652,7 @@
         <v>59-66</v>
       </c>
       <c r="G91" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H91" s="1">
         <v>0.333</v>
@@ -4699,7 +4699,7 @@
         <v>59-66</v>
       </c>
       <c r="G92" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H92" s="1">
         <v>0.334</v>
@@ -4746,13 +4746,13 @@
         <v>47-54</v>
       </c>
       <c r="G93" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H93" s="1">
         <v>0.4</v>
       </c>
-      <c r="I93" t="str">
-        <v/>
+      <c r="I93" s="1">
+        <v>0.25</v>
       </c>
       <c r="J93" t="str">
         <v>Yes</v>
@@ -4793,7 +4793,7 @@
         <v>47-54</v>
       </c>
       <c r="G94" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H94" s="1">
         <v>0.2</v>
@@ -4840,7 +4840,7 @@
         <v>47-54</v>
       </c>
       <c r="G95" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H95" s="1">
         <v>0.2</v>
@@ -4887,7 +4887,7 @@
         <v>47-54</v>
       </c>
       <c r="G96" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H96" s="1">
         <v>0.2</v>
@@ -4934,7 +4934,7 @@
         <v>53-60</v>
       </c>
       <c r="G97" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H97" s="1">
         <v>0.3</v>
@@ -4981,7 +4981,7 @@
         <v>53-60</v>
       </c>
       <c r="G98" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H98" s="1">
         <v>0.35</v>
@@ -5028,7 +5028,7 @@
         <v>53-60</v>
       </c>
       <c r="G99" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H99" s="1">
         <v>0.35</v>
@@ -5075,13 +5075,13 @@
         <v>38-43</v>
       </c>
       <c r="G100" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H100" s="1">
         <v>0.7</v>
       </c>
-      <c r="I100" t="str">
-        <v/>
+      <c r="I100" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J100" t="str">
         <v>Yes</v>
@@ -5122,13 +5122,13 @@
         <v>40-45</v>
       </c>
       <c r="G101" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H101" s="1">
         <v>0.15</v>
       </c>
-      <c r="I101" t="str">
-        <v/>
+      <c r="I101" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J101" t="str">
         <v>Yes</v>
@@ -5169,13 +5169,13 @@
         <v>38-43</v>
       </c>
       <c r="G102" t="str">
-        <v>36-40</v>
+        <v>35-38</v>
       </c>
       <c r="H102" s="1">
         <v>0.15</v>
       </c>
-      <c r="I102" t="str">
-        <v/>
+      <c r="I102" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J102" t="str">
         <v>Yes</v>
@@ -5216,7 +5216,7 @@
         <v>44-48</v>
       </c>
       <c r="G103" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H103" s="1">
         <v>0.2</v>
@@ -5263,7 +5263,7 @@
         <v>44-48</v>
       </c>
       <c r="G104" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H104" s="1">
         <v>0.2</v>
@@ -5310,7 +5310,7 @@
         <v>48-52</v>
       </c>
       <c r="G105" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H105" s="1">
         <v>0.2</v>
@@ -5357,7 +5357,7 @@
         <v>44-48</v>
       </c>
       <c r="G106" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H106" s="1">
         <v>0.15</v>
@@ -5404,7 +5404,7 @@
         <v>48-52</v>
       </c>
       <c r="G107" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H107" s="1">
         <v>0.15</v>
@@ -5451,7 +5451,7 @@
         <v>50-55</v>
       </c>
       <c r="G108" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H108" s="1">
         <v>0.1</v>
@@ -5498,7 +5498,7 @@
         <v>48-52</v>
       </c>
       <c r="G109" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H109" s="1">
         <v>0.2</v>
@@ -5545,7 +5545,7 @@
         <v>48-52</v>
       </c>
       <c r="G110" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H110" s="1">
         <v>0.2</v>
@@ -5592,7 +5592,7 @@
         <v>50-55</v>
       </c>
       <c r="G111" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H111" s="1">
         <v>0.1</v>
@@ -5639,7 +5639,7 @@
         <v>50-55</v>
       </c>
       <c r="G112" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H112" s="1">
         <v>0.1</v>
@@ -5686,7 +5686,7 @@
         <v>50-55</v>
       </c>
       <c r="G113" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H113" s="1">
         <v>0.1</v>
@@ -5733,7 +5733,7 @@
         <v>53-58</v>
       </c>
       <c r="G114" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H114" s="1">
         <v>0.1</v>
@@ -5780,7 +5780,7 @@
         <v>50-55</v>
       </c>
       <c r="G115" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H115" s="1">
         <v>0.1</v>
@@ -5827,7 +5827,7 @@
         <v>53-58</v>
       </c>
       <c r="G116" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H116" s="1">
         <v>0.1</v>
@@ -5874,7 +5874,7 @@
         <v>50-55</v>
       </c>
       <c r="G117" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H117" s="1">
         <v>0.15</v>
@@ -5921,7 +5921,7 @@
         <v>50-55</v>
       </c>
       <c r="G118" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H118" s="1">
         <v>0.1</v>
@@ -5968,7 +5968,7 @@
         <v>55-60</v>
       </c>
       <c r="G119" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H119" s="1">
         <v>0.05</v>
@@ -6015,7 +6015,7 @@
         <v>50-55</v>
       </c>
       <c r="G120" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H120" s="1">
         <v>0.15</v>
@@ -6062,7 +6062,7 @@
         <v>50-55</v>
       </c>
       <c r="G121" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H121" s="1">
         <v>0.15</v>
@@ -6109,7 +6109,7 @@
         <v>50-55</v>
       </c>
       <c r="G122" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H122" s="1">
         <v>0.2</v>
@@ -6156,7 +6156,7 @@
         <v>55-60</v>
       </c>
       <c r="G123" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H123" s="1">
         <v>0.2</v>
@@ -6203,7 +6203,7 @@
         <v>50-55</v>
       </c>
       <c r="G124" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H124" s="1">
         <v>0.25</v>
@@ -6250,13 +6250,13 @@
         <v>55-60</v>
       </c>
       <c r="G125" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H125" s="1">
         <v>0.05</v>
       </c>
-      <c r="I125" t="str">
-        <v/>
+      <c r="I125" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J125" t="str">
         <v>Yes</v>
@@ -6297,7 +6297,7 @@
         <v>50-55</v>
       </c>
       <c r="G126" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H126" s="1">
         <v>0.15</v>
@@ -6344,7 +6344,7 @@
         <v>50-55</v>
       </c>
       <c r="G127" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H127" s="1">
         <v>0.15</v>
@@ -6391,7 +6391,7 @@
         <v>50-55</v>
       </c>
       <c r="G128" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H128" s="1">
         <v>0.2</v>
@@ -6438,7 +6438,7 @@
         <v>55-60</v>
       </c>
       <c r="G129" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H129" s="1">
         <v>0.2</v>
@@ -6485,7 +6485,7 @@
         <v>56-62</v>
       </c>
       <c r="G130" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H130" s="1">
         <v>0.25</v>
@@ -6532,7 +6532,7 @@
         <v>56-62</v>
       </c>
       <c r="G131" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H131" s="1">
         <v>0.25</v>
@@ -6579,7 +6579,7 @@
         <v>56-62</v>
       </c>
       <c r="G132" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6626,7 +6626,7 @@
         <v>58-64</v>
       </c>
       <c r="G133" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H133" s="1">
         <v>0.15</v>
@@ -6673,7 +6673,7 @@
         <v>60-66</v>
       </c>
       <c r="G134" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H134" s="1">
         <v>0.15</v>
@@ -6720,7 +6720,7 @@
         <v>60-66</v>
       </c>
       <c r="G135" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H135" s="1">
         <v>0.1</v>
@@ -6767,7 +6767,7 @@
         <v>60-66</v>
       </c>
       <c r="G136" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H136" s="1">
         <v>0.1</v>
@@ -6814,7 +6814,7 @@
         <v>63-70</v>
       </c>
       <c r="G137" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H137" s="1">
         <v>0.15</v>
@@ -6861,7 +6861,7 @@
         <v>62-69</v>
       </c>
       <c r="G138" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H138" s="1">
         <v>0.15</v>
@@ -6908,7 +6908,7 @@
         <v>62-69</v>
       </c>
       <c r="G139" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H139" s="1">
         <v>0.1</v>
@@ -6955,7 +6955,7 @@
         <v>63-70</v>
       </c>
       <c r="G140" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H140" s="1">
         <v>0.1</v>
@@ -7002,7 +7002,7 @@
         <v>62-69</v>
       </c>
       <c r="G141" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7049,7 +7049,7 @@
         <v>65-72</v>
       </c>
       <c r="G142" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H142" s="1">
         <v>0.1</v>
@@ -7096,7 +7096,7 @@
         <v>65-72</v>
       </c>
       <c r="G143" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H143" s="1">
         <v>0.05</v>
@@ -7143,7 +7143,7 @@
         <v>65-72</v>
       </c>
       <c r="G144" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H144" s="1">
         <v>0.05</v>
@@ -7190,13 +7190,13 @@
         <v>68-75</v>
       </c>
       <c r="G145" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H145" s="1">
         <v>0.3</v>
       </c>
-      <c r="I145" t="str">
-        <v/>
+      <c r="I145" s="1">
+        <v>0.1</v>
       </c>
       <c r="J145" t="str">
         <v>Yes</v>
@@ -7237,7 +7237,7 @@
         <v>71-78</v>
       </c>
       <c r="G146" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H146" s="1">
         <v>0.1</v>
@@ -7284,7 +7284,7 @@
         <v>68-75</v>
       </c>
       <c r="G147" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H147" s="1">
         <v>0.15</v>
@@ -7331,7 +7331,7 @@
         <v>71-78</v>
       </c>
       <c r="G148" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H148" s="1">
         <v>0.1</v>
@@ -7378,7 +7378,7 @@
         <v>68-75</v>
       </c>
       <c r="G149" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H149" s="1">
         <v>0.05</v>
@@ -7425,7 +7425,7 @@
         <v>71-78</v>
       </c>
       <c r="G150" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H150" s="1">
         <v>0.05</v>
@@ -7472,7 +7472,7 @@
         <v>68-75</v>
       </c>
       <c r="G151" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H151" s="1">
         <v>0.1</v>
@@ -7519,7 +7519,7 @@
         <v>71-78</v>
       </c>
       <c r="G152" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H152" s="1">
         <v>0.025</v>
@@ -7566,7 +7566,7 @@
         <v>68-75</v>
       </c>
       <c r="G153" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H153" s="1">
         <v>0.1</v>
@@ -7613,7 +7613,7 @@
         <v>71-78</v>
       </c>
       <c r="G154" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H154" s="1">
         <v>0.025</v>
@@ -7660,7 +7660,7 @@
         <v>75-83</v>
       </c>
       <c r="G155" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H155" s="1">
         <v>0.2</v>
@@ -7707,7 +7707,7 @@
         <v>75-83</v>
       </c>
       <c r="G156" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H156" s="1">
         <v>0.2</v>
@@ -7754,7 +7754,7 @@
         <v>77-85</v>
       </c>
       <c r="G157" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H157" s="1">
         <v>0.15</v>
@@ -7801,7 +7801,7 @@
         <v>77-85</v>
       </c>
       <c r="G158" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H158" s="1">
         <v>0.15</v>
@@ -7848,7 +7848,7 @@
         <v>79-87</v>
       </c>
       <c r="G159" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H159" s="1">
         <v>0.13</v>
@@ -7895,13 +7895,13 @@
         <v>90-90</v>
       </c>
       <c r="G160" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H160" s="1">
         <v>0.02</v>
       </c>
-      <c r="I160" t="str">
-        <v/>
+      <c r="I160" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J160" t="str">
         <v>Legacy</v>
@@ -7942,7 +7942,7 @@
         <v>77-85</v>
       </c>
       <c r="G161" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H161" s="1">
         <v>0.15</v>
@@ -7989,7 +7989,7 @@
         <v>72-79</v>
       </c>
       <c r="G162" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H162" s="1">
         <v>0.2</v>
@@ -8036,7 +8036,7 @@
         <v>72-79</v>
       </c>
       <c r="G163" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H163" s="1">
         <v>0.15</v>
@@ -8083,7 +8083,7 @@
         <v>75-82</v>
       </c>
       <c r="G164" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H164" s="1">
         <v>0.2</v>
@@ -8130,7 +8130,7 @@
         <v>75-82</v>
       </c>
       <c r="G165" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H165" s="1">
         <v>0.15</v>
@@ -8177,7 +8177,7 @@
         <v>75-82</v>
       </c>
       <c r="G166" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H166" s="1">
         <v>0.2</v>
@@ -8224,7 +8224,7 @@
         <v>77-84</v>
       </c>
       <c r="G167" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H167" s="1">
         <v>0.05</v>
@@ -8271,7 +8271,7 @@
         <v>77-84</v>
       </c>
       <c r="G168" t="str">
-        <v>47-52</v>
+        <v>47-51</v>
       </c>
       <c r="H168" s="1">
         <v>0.05</v>
@@ -8318,7 +8318,7 @@
         <v>69-74</v>
       </c>
       <c r="G169" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H169" s="1">
         <v>0.2</v>
@@ -8365,7 +8365,7 @@
         <v>69-74</v>
       </c>
       <c r="G170" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H170" s="1">
         <v>0.2</v>
@@ -8412,7 +8412,7 @@
         <v>73-78</v>
       </c>
       <c r="G171" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H171" s="1">
         <v>0.2</v>
@@ -8459,7 +8459,7 @@
         <v>71-78</v>
       </c>
       <c r="G172" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H172" s="1">
         <v>0.15</v>
@@ -8506,7 +8506,7 @@
         <v>73-80</v>
       </c>
       <c r="G173" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H173" s="1">
         <v>0.15</v>
@@ -8553,7 +8553,7 @@
         <v>72-79</v>
       </c>
       <c r="G174" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H174" s="1">
         <v>0.08</v>
@@ -8600,13 +8600,13 @@
         <v>85-85</v>
       </c>
       <c r="G175" t="str">
-        <v>47-52</v>
+        <v>96-104</v>
       </c>
       <c r="H175" s="1">
         <v>0.02</v>
       </c>
-      <c r="I175" t="str">
-        <v/>
+      <c r="I175" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J175" t="str">
         <v>Legacy</v>
@@ -8647,7 +8647,7 @@
         <v>81-88</v>
       </c>
       <c r="G176" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H176" s="1">
         <v>0.15</v>
@@ -8694,7 +8694,7 @@
         <v>79-86</v>
       </c>
       <c r="G177" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H177" s="1">
         <v>0.15</v>
@@ -8741,7 +8741,7 @@
         <v>77-84</v>
       </c>
       <c r="G178" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H178" s="1">
         <v>0.2</v>
@@ -8788,7 +8788,7 @@
         <v>77-84</v>
       </c>
       <c r="G179" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H179" s="1">
         <v>0.2</v>
@@ -8835,7 +8835,7 @@
         <v>79-86</v>
       </c>
       <c r="G180" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H180" s="1">
         <v>0.15</v>
@@ -8882,7 +8882,7 @@
         <v>79-86</v>
       </c>
       <c r="G181" t="str">
-        <v>49-54</v>
+        <v>49-53</v>
       </c>
       <c r="H181" s="1">
         <v>0.15</v>
@@ -8929,7 +8929,7 @@
         <v>83-91</v>
       </c>
       <c r="G182" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H182" s="1">
         <v>0.25</v>
@@ -8976,7 +8976,7 @@
         <v>83-91</v>
       </c>
       <c r="G183" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H183" s="1">
         <v>0.125</v>
@@ -9023,7 +9023,7 @@
         <v>83-91</v>
       </c>
       <c r="G184" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H184" s="1">
         <v>0.125</v>
@@ -9070,7 +9070,7 @@
         <v>83-91</v>
       </c>
       <c r="G185" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H185" s="1">
         <v>0.2</v>
@@ -9117,7 +9117,7 @@
         <v>87-95</v>
       </c>
       <c r="G186" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H186" s="1">
         <v>0.15</v>
@@ -9164,7 +9164,7 @@
         <v>87-95</v>
       </c>
       <c r="G187" t="str">
-        <v>52-58</v>
+        <v>51-56</v>
       </c>
       <c r="H187" s="1">
         <v>0.15</v>
@@ -9211,7 +9211,7 @@
         <v>82-90</v>
       </c>
       <c r="G188" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H188" s="1">
         <v>0.25</v>
@@ -9258,7 +9258,7 @@
         <v>85-93</v>
       </c>
       <c r="G189" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H189" s="1">
         <v>0.25</v>
@@ -9305,7 +9305,7 @@
         <v>80-87</v>
       </c>
       <c r="G190" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H190" s="1">
         <v>0.23</v>
@@ -9352,7 +9352,7 @@
         <v>85-93</v>
       </c>
       <c r="G191" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H191" s="1">
         <v>0.15</v>
@@ -9399,7 +9399,7 @@
         <v>85-93</v>
       </c>
       <c r="G192" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H192" s="1">
         <v>0.1</v>
@@ -9446,13 +9446,13 @@
         <v>95-95</v>
       </c>
       <c r="G193" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H193" s="1">
         <v>0.02</v>
       </c>
-      <c r="I193" t="str">
-        <v/>
+      <c r="I193" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J193" t="str">
         <v>Legacy</v>
@@ -9493,7 +9493,7 @@
         <v>87-95</v>
       </c>
       <c r="G194" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H194" s="1">
         <v>0.2</v>
@@ -9540,7 +9540,7 @@
         <v>87-95</v>
       </c>
       <c r="G195" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H195" s="1">
         <v>0.15</v>
@@ -9587,7 +9587,7 @@
         <v>90-98</v>
       </c>
       <c r="G196" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H196" s="1">
         <v>0.15</v>
@@ -9634,7 +9634,7 @@
         <v>90-98</v>
       </c>
       <c r="G197" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H197" s="1">
         <v>0.15</v>
@@ -9681,7 +9681,7 @@
         <v>89-97</v>
       </c>
       <c r="G198" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H198" s="1">
         <v>0.15</v>
@@ -9728,7 +9728,7 @@
         <v>90-98</v>
       </c>
       <c r="G199" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H199" s="1">
         <v>0.19</v>
@@ -9775,13 +9775,13 @@
         <v>100-100</v>
       </c>
       <c r="G200" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H200" s="1">
         <v>0.01</v>
       </c>
-      <c r="I200" t="str">
-        <v/>
+      <c r="I200" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J200" t="str">
         <v>Legacy</v>
@@ -9822,13 +9822,13 @@
         <v>41-48</v>
       </c>
       <c r="G201" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H201" s="1">
         <v>0.7</v>
       </c>
-      <c r="I201" t="str">
-        <v/>
+      <c r="I201" s="1">
+        <v>0.25</v>
       </c>
       <c r="J201" t="str">
         <v/>
@@ -9869,13 +9869,13 @@
         <v>41-48</v>
       </c>
       <c r="G202" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H202" s="1">
         <v>0.15</v>
       </c>
-      <c r="I202" t="str">
-        <v/>
+      <c r="I202" s="1">
+        <v>0.25</v>
       </c>
       <c r="J202" t="str">
         <v/>
@@ -9916,13 +9916,13 @@
         <v>41-48</v>
       </c>
       <c r="G203" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H203" s="1">
         <v>0.08</v>
       </c>
-      <c r="I203" t="str">
-        <v/>
+      <c r="I203" s="1">
+        <v>0.25</v>
       </c>
       <c r="J203" t="str">
         <v/>
@@ -9963,13 +9963,13 @@
         <v>41-48</v>
       </c>
       <c r="G204" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H204" s="1">
         <v>0.07</v>
       </c>
-      <c r="I204" t="str">
-        <v/>
+      <c r="I204" s="1">
+        <v>0.25</v>
       </c>
       <c r="J204" t="str">
         <v/>
@@ -10010,7 +10010,7 @@
         <v>53-60</v>
       </c>
       <c r="G205" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H205" s="1">
         <v>0.18</v>
@@ -10057,7 +10057,7 @@
         <v>57-64</v>
       </c>
       <c r="G206" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H206" s="1">
         <v>0.05</v>
@@ -10104,13 +10104,13 @@
         <v>60-67</v>
       </c>
       <c r="G207" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H207" s="1">
         <v>0.02</v>
       </c>
-      <c r="I207" t="str">
-        <v/>
+      <c r="I207" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -10151,13 +10151,13 @@
         <v>60-67</v>
       </c>
       <c r="G208" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H208" s="1">
         <v>0.25</v>
       </c>
-      <c r="I208" t="str">
-        <v/>
+      <c r="I208" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -10198,7 +10198,7 @@
         <v>53-60</v>
       </c>
       <c r="G209" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H209" s="1">
         <v>0.2</v>
@@ -10245,7 +10245,7 @@
         <v>53-60</v>
       </c>
       <c r="G210" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H210" s="1">
         <v>0.15</v>
@@ -10292,7 +10292,7 @@
         <v>57-64</v>
       </c>
       <c r="G211" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H211" s="1">
         <v>0.15</v>
@@ -10339,7 +10339,7 @@
         <v>60-67</v>
       </c>
       <c r="G212" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H212" s="1">
         <v>0.2</v>
@@ -10386,13 +10386,13 @@
         <v>55-62</v>
       </c>
       <c r="G213" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H213" s="1">
         <v>0.3</v>
       </c>
-      <c r="I213" t="str">
-        <v/>
+      <c r="I213" s="1">
+        <v>0.2</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v>55-62</v>
       </c>
       <c r="G214" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H214" s="1">
         <v>0.3</v>
       </c>
-      <c r="I214" t="str">
-        <v/>
+      <c r="I214" s="1">
+        <v>0.2</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -10480,13 +10480,13 @@
         <v>58-65</v>
       </c>
       <c r="G215" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H215" s="1">
         <v>0.1</v>
       </c>
-      <c r="I215" t="str">
-        <v/>
+      <c r="I215" s="1">
+        <v>0.2</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -10527,13 +10527,13 @@
         <v>58-65</v>
       </c>
       <c r="G216" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H216" s="1">
         <v>0.1</v>
       </c>
-      <c r="I216" t="str">
-        <v/>
+      <c r="I216" s="1">
+        <v>0.2</v>
       </c>
       <c r="J216" t="str">
         <v/>
@@ -10574,13 +10574,13 @@
         <v>47-54</v>
       </c>
       <c r="G217" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H217" s="1">
         <v>0.4</v>
       </c>
-      <c r="I217" t="str">
-        <v/>
+      <c r="I217" s="1">
+        <v>0.25</v>
       </c>
       <c r="J217" t="str">
         <v>Yes</v>
@@ -10621,13 +10621,13 @@
         <v>47-54</v>
       </c>
       <c r="G218" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H218" s="1">
         <v>0.4</v>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="1">
+        <v>0.25</v>
       </c>
       <c r="J218" t="str">
         <v>Yes</v>
@@ -10668,13 +10668,13 @@
         <v>47-54</v>
       </c>
       <c r="G219" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H219" s="1">
         <v>0.1</v>
       </c>
-      <c r="I219" t="str">
-        <v/>
+      <c r="I219" s="1">
+        <v>0.25</v>
       </c>
       <c r="J219" t="str">
         <v>Yes</v>
@@ -10715,13 +10715,13 @@
         <v>47-54</v>
       </c>
       <c r="G220" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H220" s="1">
         <v>0.1</v>
       </c>
-      <c r="I220" t="str">
-        <v/>
+      <c r="I220" s="1">
+        <v>0.25</v>
       </c>
       <c r="J220" t="str">
         <v>Yes</v>
@@ -10762,7 +10762,7 @@
         <v>64-71</v>
       </c>
       <c r="G221" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H221" s="1">
         <v>0.25</v>
@@ -10809,7 +10809,7 @@
         <v>64-71</v>
       </c>
       <c r="G222" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H222" s="1">
         <v>0.25</v>
@@ -10856,7 +10856,7 @@
         <v>64-71</v>
       </c>
       <c r="G223" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H223" s="1">
         <v>0.25</v>
@@ -10903,7 +10903,7 @@
         <v>64-71</v>
       </c>
       <c r="G224" t="str">
-        <v>52-58</v>
+        <v>96-104</v>
       </c>
       <c r="H224" s="1">
         <v>0.25</v>
@@ -10950,7 +10950,7 @@
         <v>120-120</v>
       </c>
       <c r="G225" t="str">
-        <v>52-58</v>
+        <v>120-120</v>
       </c>
       <c r="H225" s="1">
         <v>0.2</v>
@@ -10997,7 +10997,7 @@
         <v>110-110</v>
       </c>
       <c r="G226" t="str">
-        <v>52-58</v>
+        <v>110-110</v>
       </c>
       <c r="H226" s="1">
         <v>0.2</v>
@@ -11044,7 +11044,7 @@
         <v>110-110</v>
       </c>
       <c r="G227" t="str">
-        <v>52-58</v>
+        <v>110-110</v>
       </c>
       <c r="H227" s="1">
         <v>0.2</v>
@@ -11091,7 +11091,7 @@
         <v>110-110</v>
       </c>
       <c r="G228" t="str">
-        <v>52-58</v>
+        <v>110-110</v>
       </c>
       <c r="H228" s="1">
         <v>0.2</v>
@@ -11138,7 +11138,7 @@
         <v>120-120</v>
       </c>
       <c r="G229" t="str">
-        <v>52-58</v>
+        <v>120-120</v>
       </c>
       <c r="H229" s="1">
         <v>0.2</v>

--- a/1_Kanto_Data.xlsx
+++ b/1_Kanto_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O229"/>
+  <dimension ref="A1:O243"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C4" t="str">
         <v>Route 1</v>
@@ -581,10 +581,10 @@
         <v>Yes</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Route 2</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 1","count":25}}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -639,10 +639,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C6" t="str">
         <v>Route 2</v>
@@ -675,10 +675,10 @@
         <v>Yes</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Viridian Forest</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -686,10 +686,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C7" t="str">
         <v>Route 2</v>
@@ -722,10 +722,10 @@
         <v>Yes</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Viridian Forest</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -733,10 +733,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C8" t="str">
         <v>Route 2</v>
@@ -769,10 +769,10 @@
         <v>Yes</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Viridian Forest</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C10" t="str">
         <v>Viridian Forest</v>
@@ -863,10 +863,10 @@
         <v>Yes</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Pewter Gym</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Bug","quality":"Rare","count":1}}</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C11" t="str">
         <v>Viridian Forest</v>
@@ -910,10 +910,10 @@
         <v>Yes</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Pewter Gym</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Bug","quality":"Rare","count":1}}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -921,10 +921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C12" t="str">
         <v>Viridian Forest</v>
@@ -957,10 +957,10 @@
         <v>Yes</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Pewter Gym</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Bug","quality":"Rare","count":1}}</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -968,10 +968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C13" t="str">
         <v>Viridian Forest</v>
@@ -1004,10 +1004,10 @@
         <v>Yes</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Pewter Gym</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Bug","quality":"Rare","count":1}}</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1039,7 +1039,7 @@
         <v>0.25</v>
       </c>
       <c r="I14" s="1">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C15" t="str">
         <v>Route 3</v>
@@ -1086,7 +1086,7 @@
         <v>0.25</v>
       </c>
       <c r="I15" s="1">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="J15" t="str">
         <v>Legacy</v>
@@ -1098,10 +1098,10 @@
         <v>Yes</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C16" t="str">
         <v>Route 3</v>
@@ -1145,10 +1145,10 @@
         <v>Yes</v>
       </c>
       <c r="M16" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N16" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C17" t="str">
         <v>Route 3</v>
@@ -1192,10 +1192,10 @@
         <v>Yes</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C18" t="str">
         <v>Route 3</v>
@@ -1239,10 +1239,10 @@
         <v>Yes</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C19" t="str">
         <v>Route 3</v>
@@ -1274,7 +1274,7 @@
         <v>0.02</v>
       </c>
       <c r="I19" s="1">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="J19" t="str">
         <v>Yes</v>
@@ -1286,10 +1286,10 @@
         <v>Yes</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C20" t="str">
         <v>Route 3</v>
@@ -1320,8 +1320,8 @@
       <c r="H20" s="1">
         <v>0.04</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20" s="1">
+        <v>0.13</v>
       </c>
       <c r="J20" t="str">
         <v>Yes</v>
@@ -1333,10 +1333,10 @@
         <v>Yes</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C21" t="str">
         <v>Route 3</v>
@@ -1380,10 +1380,10 @@
         <v>Yes</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Mount Moon</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ekans","count":1},{"species":"Sandshrew","count":1}]}</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C23" t="str">
         <v>Mount Moon</v>
@@ -1474,10 +1474,10 @@
         <v>Yes</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Clefairy","count":1}],"catchSpeciesByQuality":[{"species":"Zubat","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C24" t="str">
         <v>Mount Moon</v>
@@ -1508,8 +1508,8 @@
       <c r="H24" s="1">
         <v>0.15</v>
       </c>
-      <c r="I24" t="str">
-        <v/>
+      <c r="I24" s="1">
+        <v>0.2</v>
       </c>
       <c r="J24" t="str">
         <v>Yes</v>
@@ -1521,10 +1521,10 @@
         <v>Yes</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Clefairy","count":1}],"catchSpeciesByQuality":[{"species":"Zubat","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C25" t="str">
         <v>Mount Moon</v>
@@ -1568,10 +1568,10 @@
         <v>Yes</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Clefairy","count":1}],"catchSpeciesByQuality":[{"species":"Zubat","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C26" t="str">
         <v>Mount Moon</v>
@@ -1615,10 +1615,10 @@
         <v>Yes</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>Route 4</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Clefairy","count":1}],"catchSpeciesByQuality":[{"species":"Zubat","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C28" t="str">
         <v>Route 4</v>
@@ -1709,10 +1709,10 @@
         <v>Yes</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>Cerulean Gym</v>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mankey","count":2}]}</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C29" t="str">
         <v>Route 4</v>
@@ -1743,8 +1743,8 @@
       <c r="H29" s="1">
         <v>0.15</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
+      <c r="I29" s="1">
+        <v>0.2</v>
       </c>
       <c r="J29" t="str">
         <v>Yes</v>
@@ -1756,10 +1756,10 @@
         <v>Yes</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>Cerulean Gym</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mankey","count":2}]}</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C30" t="str">
         <v>Route 4</v>
@@ -1790,8 +1790,8 @@
       <c r="H30" s="1">
         <v>0.15</v>
       </c>
-      <c r="I30" t="str">
-        <v/>
+      <c r="I30" s="1">
+        <v>0.2</v>
       </c>
       <c r="J30" t="str">
         <v>Legacy</v>
@@ -1803,10 +1803,10 @@
         <v>Yes</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>Cerulean Gym</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mankey","count":2}]}</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C31" t="str">
         <v>Route 4</v>
@@ -1850,10 +1850,10 @@
         <v>Yes</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>Cerulean Gym</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mankey","count":2}]}</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C33" t="str">
         <v>Route 24</v>
@@ -1944,10 +1944,10 @@
         <v>Yes</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>Route 25</v>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":2}]}</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C34" t="str">
         <v>Route 24</v>
@@ -1991,10 +1991,10 @@
         <v>Yes</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>Route 25</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":2}]}</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C35" t="str">
         <v>Route 24</v>
@@ -2025,8 +2025,8 @@
       <c r="H35" s="1">
         <v>0.15</v>
       </c>
-      <c r="I35" t="str">
-        <v/>
+      <c r="I35" s="1">
+        <v>0.2</v>
       </c>
       <c r="J35" t="str">
         <v>Yes</v>
@@ -2038,10 +2038,10 @@
         <v>Yes</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Route 25</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":2}]}</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C36" t="str">
         <v>Route 24</v>
@@ -2072,8 +2072,8 @@
       <c r="H36" s="1">
         <v>0.15</v>
       </c>
-      <c r="I36" t="str">
-        <v/>
+      <c r="I36" s="1">
+        <v>0.2</v>
       </c>
       <c r="J36" t="str">
         <v>Legacy</v>
@@ -2085,10 +2085,10 @@
         <v>Yes</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>Route 25</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":2}]}</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C38" t="str">
         <v>Route 25</v>
@@ -2179,10 +2179,10 @@
         <v>Yes</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Route 5, Daycare</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":5}]}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C39" t="str">
         <v>Route 25</v>
@@ -2226,10 +2226,10 @@
         <v>Yes</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Route 5, Daycare</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":5}]}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C40" t="str">
         <v>Route 25</v>
@@ -2260,8 +2260,8 @@
       <c r="H40" s="1">
         <v>0.15</v>
       </c>
-      <c r="I40" t="str">
-        <v/>
+      <c r="I40" s="1">
+        <v>0.2</v>
       </c>
       <c r="J40" t="str">
         <v>Yes</v>
@@ -2273,10 +2273,10 @@
         <v>Yes</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>Route 5, Daycare</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":5}]}</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C41" t="str">
         <v>Route 25</v>
@@ -2307,8 +2307,8 @@
       <c r="H41" s="1">
         <v>0.15</v>
       </c>
-      <c r="I41" t="str">
-        <v/>
+      <c r="I41" s="1">
+        <v>0.2</v>
       </c>
       <c r="J41" t="str">
         <v>Yes</v>
@@ -2320,10 +2320,10 @@
         <v>Yes</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>Route 5, Daycare</v>
       </c>
       <c r="N41" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Abra","count":5}]}</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C43" t="str">
         <v>Route 5</v>
@@ -2414,10 +2414,10 @@
         <v>Yes</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Route 6</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 5","count":100}}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C44" t="str">
         <v>Route 5</v>
@@ -2461,10 +2461,10 @@
         <v>Yes</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>Route 6</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 5","count":100}}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C45" t="str">
         <v>Route 5</v>
@@ -2508,10 +2508,10 @@
         <v>Yes</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>Route 6</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 5","count":100}}</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2543,7 +2543,7 @@
         <v>0.3</v>
       </c>
       <c r="I46" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J46" t="str">
         <v>Yes</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C47" t="str">
         <v>Route 6</v>
@@ -2590,7 +2590,7 @@
         <v>0.3</v>
       </c>
       <c r="I47" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J47" t="str">
         <v>Yes</v>
@@ -2602,10 +2602,10 @@
         <v>Yes</v>
       </c>
       <c r="M47" t="str">
-        <v/>
+        <v>Vermilion Gym</v>
       </c>
       <c r="N47" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Psyduck","count":1},{"species":"Goldeen","count":1}]}</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C48" t="str">
         <v>Route 6</v>
@@ -2649,10 +2649,10 @@
         <v>Yes</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>Vermilion Gym</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Psyduck","count":1},{"species":"Goldeen","count":1}]}</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C49" t="str">
         <v>Route 6</v>
@@ -2696,10 +2696,10 @@
         <v>Yes</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>Vermilion Gym</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Psyduck","count":1},{"species":"Goldeen","count":1}]}</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C50" t="str">
         <v>Route 6</v>
@@ -2731,7 +2731,7 @@
         <v>0.05</v>
       </c>
       <c r="I50" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J50" t="str">
         <v>Yes</v>
@@ -2743,10 +2743,10 @@
         <v>Yes</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>Vermilion Gym</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Psyduck","count":1},{"species":"Goldeen","count":1}]}</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="C51" t="str">
         <v>Route 6</v>
@@ -2778,7 +2778,7 @@
         <v>0.05</v>
       </c>
       <c r="I51" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J51" t="str">
         <v>Legacy</v>
@@ -2790,10 +2790,10 @@
         <v>Yes</v>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>Vermilion Gym</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Psyduck","count":1},{"species":"Goldeen","count":1}]}</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2825,7 +2825,7 @@
         <v>0.4</v>
       </c>
       <c r="I52" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J52" t="str">
         <v>Legacy</v>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C53" t="str">
         <v>Route 11</v>
@@ -2871,8 +2871,8 @@
       <c r="H53" s="1">
         <v>0.25</v>
       </c>
-      <c r="I53" t="str">
-        <v/>
+      <c r="I53" s="1">
+        <v>0.17</v>
       </c>
       <c r="J53" t="str">
         <v>Yes</v>
@@ -2884,10 +2884,10 @@
         <v>Yes</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>Digglett Cave</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Drowzee","count":5},{"species":"Raticate","count":1}]}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C54" t="str">
         <v>Route 11</v>
@@ -2918,8 +2918,8 @@
       <c r="H54" s="1">
         <v>0.1</v>
       </c>
-      <c r="I54" t="str">
-        <v/>
+      <c r="I54" s="1">
+        <v>0.17</v>
       </c>
       <c r="J54" t="str">
         <v>Legacy</v>
@@ -2931,10 +2931,10 @@
         <v>Yes</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Digglett Cave</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Drowzee","count":5},{"species":"Raticate","count":1}]}</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C55" t="str">
         <v>Route 11</v>
@@ -2966,7 +2966,7 @@
         <v>0.05</v>
       </c>
       <c r="I55" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J55" t="str">
         <v>Legacy</v>
@@ -2978,10 +2978,10 @@
         <v>Yes</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>Digglett Cave</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Drowzee","count":5},{"species":"Raticate","count":1}]}</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C56" t="str">
         <v>Route 11</v>
@@ -3012,8 +3012,8 @@
       <c r="H56" s="1">
         <v>0.1</v>
       </c>
-      <c r="I56" t="str">
-        <v/>
+      <c r="I56" s="1">
+        <v>0.17</v>
       </c>
       <c r="J56" t="str">
         <v>Yes</v>
@@ -3025,10 +3025,10 @@
         <v>Yes</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Digglett Cave</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Drowzee","count":5},{"species":"Raticate","count":1}]}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C57" t="str">
         <v>Route 11</v>
@@ -3072,10 +3072,10 @@
         <v>Yes</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>Digglett Cave</v>
       </c>
       <c r="N57" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Drowzee","count":5},{"species":"Raticate","count":1}]}</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C59" t="str">
         <v>Digglett Cave</v>
@@ -3166,10 +3166,10 @@
         <v>Yes</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Route 9</v>
       </c>
       <c r="N59" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dugtrio","count":2}]}</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C61" t="str">
         <v>Route 9</v>
@@ -3260,10 +3260,10 @@
         <v>Yes</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Route 10</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Fearow","count":2}]}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C62" t="str">
         <v>Route 9</v>
@@ -3294,8 +3294,8 @@
       <c r="H62" s="1">
         <v>0.15</v>
       </c>
-      <c r="I62" t="str">
-        <v/>
+      <c r="I62" s="1">
+        <v>0.2</v>
       </c>
       <c r="J62" t="str">
         <v>Legacy</v>
@@ -3307,10 +3307,10 @@
         <v>Yes</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>Route 10</v>
       </c>
       <c r="N62" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Fearow","count":2}]}</v>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C63" t="str">
         <v>Route 9</v>
@@ -3341,8 +3341,8 @@
       <c r="H63" s="1">
         <v>0.15</v>
       </c>
-      <c r="I63" t="str">
-        <v/>
+      <c r="I63" s="1">
+        <v>0.2</v>
       </c>
       <c r="J63" t="str">
         <v>Yes</v>
@@ -3354,10 +3354,10 @@
         <v>Yes</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>Route 10</v>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Fearow","count":2}]}</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C64" t="str">
         <v>Route 9</v>
@@ -3388,8 +3388,8 @@
       <c r="H64" s="1">
         <v>0.15</v>
       </c>
-      <c r="I64" t="str">
-        <v/>
+      <c r="I64" s="1">
+        <v>0.2</v>
       </c>
       <c r="J64" t="str">
         <v>Yes</v>
@@ -3401,10 +3401,10 @@
         <v>Yes</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>Route 10</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Fearow","count":2}]}</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C66" t="str">
         <v>Route 10</v>
@@ -3495,10 +3495,10 @@
         <v>Yes</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>Rock Tunnel</v>
       </c>
       <c r="N66" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 10","count":100}}</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C67" t="str">
         <v>Route 10</v>
@@ -3542,10 +3542,10 @@
         <v>Yes</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>Rock Tunnel</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 10","count":100}}</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C68" t="str">
         <v>Route 10</v>
@@ -3589,10 +3589,10 @@
         <v>Yes</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Rock Tunnel</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 10","count":100}}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C69" t="str">
         <v>Route 10</v>
@@ -3636,10 +3636,10 @@
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Rock Tunnel</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 10","count":100}}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C71" t="str">
         <v>Rock Tunnel</v>
@@ -3730,10 +3730,10 @@
         <v>Yes</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>Route 8</v>
       </c>
       <c r="N71" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Onix","count":2},{"species":"Machop","count":2}]}</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C72" t="str">
         <v>Rock Tunnel</v>
@@ -3777,10 +3777,10 @@
         <v>Yes</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>Route 8</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Onix","count":2},{"species":"Machop","count":2}]}</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C73" t="str">
         <v>Rock Tunnel</v>
@@ -3824,10 +3824,10 @@
         <v>Yes</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Route 8</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Onix","count":2},{"species":"Machop","count":2}]}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C75" t="str">
         <v>Route 8</v>
@@ -3918,10 +3918,10 @@
         <v>Yes</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>Celadon Gym</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kadabra","count":2}],"catchByType":{"type":"Fire","count":10}}</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C76" t="str">
         <v>Route 8</v>
@@ -3965,10 +3965,10 @@
         <v>Yes</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>Celadon Gym</v>
       </c>
       <c r="N76" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kadabra","count":2}],"catchByType":{"type":"Fire","count":10}}</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C77" t="str">
         <v>Route 8</v>
@@ -4012,10 +4012,10 @@
         <v>Yes</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>Celadon Gym</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kadabra","count":2}],"catchByType":{"type":"Fire","count":10}}</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C78" t="str">
         <v>Route 8</v>
@@ -4059,10 +4059,10 @@
         <v>Yes</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>Celadon Gym</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kadabra","count":2}],"catchByType":{"type":"Fire","count":10}}</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B80" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C80" t="str">
         <v>Route 7</v>
@@ -4153,10 +4153,10 @@
         <v>Yes</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>Pokemon Tower</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 7","count":150}}</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C81" t="str">
         <v>Route 7</v>
@@ -4200,10 +4200,10 @@
         <v>Yes</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>Pokemon Tower</v>
       </c>
       <c r="N81" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 7","count":150}}</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4211,10 +4211,10 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B82" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C82" t="str">
         <v>Route 7</v>
@@ -4247,10 +4247,10 @@
         <v>Yes</v>
       </c>
       <c r="M82" t="str">
-        <v/>
+        <v>Pokemon Tower</v>
       </c>
       <c r="N82" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 7","count":150}}</v>
       </c>
       <c r="O82" t="str">
         <v/>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C83" t="str">
         <v>Route 7</v>
@@ -4294,10 +4294,10 @@
         <v>Yes</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Pokemon Tower</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 7","count":150}}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B88" t="str">
         <v/>
@@ -4540,7 +4540,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B98" t="str">
         <v/>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>0.7</v>
       </c>
       <c r="I100" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J100" t="str">
         <v>Yes</v>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C101" t="str">
         <v>Pokemon Tower</v>
@@ -5128,7 +5128,7 @@
         <v>0.15</v>
       </c>
       <c r="I101" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J101" t="str">
         <v>Yes</v>
@@ -5140,10 +5140,10 @@
         <v>Yes</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Haunter","count":2},{"species":"Cubone","count":1}]}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C102" t="str">
         <v>Pokemon Tower</v>
@@ -5175,7 +5175,7 @@
         <v>0.15</v>
       </c>
       <c r="I102" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J102" t="str">
         <v>Yes</v>
@@ -5187,10 +5187,10 @@
         <v>Yes</v>
       </c>
       <c r="M102" t="str">
-        <v/>
+        <v>Route 12</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Haunter","count":2},{"species":"Cubone","count":1}]}</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C104" t="str">
         <v>Route 12</v>
@@ -5281,10 +5281,10 @@
         <v>Yes</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":3}]}</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C105" t="str">
         <v>Route 12</v>
@@ -5328,10 +5328,10 @@
         <v>Yes</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":3}]}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C106" t="str">
         <v>Route 12</v>
@@ -5375,10 +5375,10 @@
         <v>Yes</v>
       </c>
       <c r="M106" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N106" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":3}]}</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C107" t="str">
         <v>Route 12</v>
@@ -5422,10 +5422,10 @@
         <v>Yes</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":3}]}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C108" t="str">
         <v>Route 12</v>
@@ -5469,10 +5469,10 @@
         <v>Yes</v>
       </c>
       <c r="M108" t="str">
-        <v/>
+        <v>Route 13</v>
       </c>
       <c r="N108" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":3}]}</v>
       </c>
       <c r="O108" t="str">
         <v/>
@@ -5503,8 +5503,8 @@
       <c r="H109" s="1">
         <v>0.2</v>
       </c>
-      <c r="I109" t="str">
-        <v/>
+      <c r="I109" s="1">
+        <v>0.13</v>
       </c>
       <c r="J109" t="str">
         <v>Yes</v>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C110" t="str">
         <v>Route 13</v>
@@ -5550,8 +5550,8 @@
       <c r="H110" s="1">
         <v>0.2</v>
       </c>
-      <c r="I110" t="str">
-        <v/>
+      <c r="I110" s="1">
+        <v>0.13</v>
       </c>
       <c r="J110" t="str">
         <v>Yes</v>
@@ -5563,10 +5563,10 @@
         <v>Yes</v>
       </c>
       <c r="M110" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C111" t="str">
         <v>Route 13</v>
@@ -5610,10 +5610,10 @@
         <v>Yes</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C112" t="str">
         <v>Route 13</v>
@@ -5657,10 +5657,10 @@
         <v>Yes</v>
       </c>
       <c r="M112" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O112" t="str">
         <v/>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C113" t="str">
         <v>Route 13</v>
@@ -5704,10 +5704,10 @@
         <v>Yes</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C114" t="str">
         <v>Route 13</v>
@@ -5751,10 +5751,10 @@
         <v>Yes</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O114" t="str">
         <v/>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C115" t="str">
         <v>Route 13</v>
@@ -5798,10 +5798,10 @@
         <v>Yes</v>
       </c>
       <c r="M115" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N115" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C116" t="str">
         <v>Route 13</v>
@@ -5845,10 +5845,10 @@
         <v>Yes</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>Route 14,15</v>
       </c>
       <c r="N116" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Victreebel","count":1},{"species":"Vileplume","count":1}]}</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -5973,8 +5973,8 @@
       <c r="H119" s="1">
         <v>0.05</v>
       </c>
-      <c r="I119" t="str">
-        <v/>
+      <c r="I119" s="1">
+        <v>0.14</v>
       </c>
       <c r="J119" t="str">
         <v>Yes</v>
@@ -6114,8 +6114,8 @@
       <c r="H122" s="1">
         <v>0.2</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
+      <c r="I122" s="1">
+        <v>0.14</v>
       </c>
       <c r="J122" t="str">
         <v>Legacy</v>
@@ -6208,8 +6208,8 @@
       <c r="H124" s="1">
         <v>0.25</v>
       </c>
-      <c r="I124" t="str">
-        <v/>
+      <c r="I124" s="1">
+        <v>0.17</v>
       </c>
       <c r="J124" t="str">
         <v>Yes</v>
@@ -6256,7 +6256,7 @@
         <v>0.05</v>
       </c>
       <c r="I125" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J125" t="str">
         <v>Yes</v>
@@ -6443,8 +6443,8 @@
       <c r="H129" s="1">
         <v>0.2</v>
       </c>
-      <c r="I129" t="str">
-        <v/>
+      <c r="I129" s="1">
+        <v>0.15</v>
       </c>
       <c r="J129" t="str">
         <v>Yes</v>
@@ -6631,8 +6631,8 @@
       <c r="H133" s="1">
         <v>0.15</v>
       </c>
-      <c r="I133" t="str">
-        <v/>
+      <c r="I133" s="1">
+        <v>0.2</v>
       </c>
       <c r="J133" t="str">
         <v>Yes</v>
@@ -6678,8 +6678,8 @@
       <c r="H134" s="1">
         <v>0.15</v>
       </c>
-      <c r="I134" t="str">
-        <v/>
+      <c r="I134" s="1">
+        <v>0.2</v>
       </c>
       <c r="J134" t="str">
         <v>Yes</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B136" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C136" t="str">
         <v>Safari Zone</v>
@@ -6785,10 +6785,10 @@
         <v>Yes</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O136" t="str">
         <v/>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C137" t="str">
         <v>Safari Zone</v>
@@ -6832,10 +6832,10 @@
         <v>Yes</v>
       </c>
       <c r="M137" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N137" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O137" t="str">
         <v/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C138" t="str">
         <v>Safari Zone</v>
@@ -6879,10 +6879,10 @@
         <v>Yes</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O138" t="str">
         <v/>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B139" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C139" t="str">
         <v>Safari Zone</v>
@@ -6926,10 +6926,10 @@
         <v>Yes</v>
       </c>
       <c r="M139" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N139" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O139" t="str">
         <v/>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B140" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C140" t="str">
         <v>Safari Zone</v>
@@ -6973,10 +6973,10 @@
         <v>Yes</v>
       </c>
       <c r="M140" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N140" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O140" t="str">
         <v/>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C141" t="str">
         <v>Safari Zone</v>
@@ -7020,10 +7020,10 @@
         <v>Yes</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C142" t="str">
         <v>Safari Zone</v>
@@ -7067,10 +7067,10 @@
         <v>Yes</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C143" t="str">
         <v>Safari Zone</v>
@@ -7114,10 +7114,10 @@
         <v>Yes</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N143" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O143" t="str">
         <v/>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C144" t="str">
         <v>Safari Zone</v>
@@ -7161,10 +7161,10 @@
         <v>Yes</v>
       </c>
       <c r="M144" t="str">
-        <v/>
+        <v>Saffron Gym</v>
       </c>
       <c r="N144" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone","count":100}}</v>
       </c>
       <c r="O144" t="str">
         <v/>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B146" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C146" t="str">
         <v>Sea Routes</v>
@@ -7255,10 +7255,10 @@
         <v>Yes</v>
       </c>
       <c r="M146" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N146" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O146" t="str">
         <v/>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B147" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C147" t="str">
         <v>Sea Routes</v>
@@ -7302,10 +7302,10 @@
         <v>Yes</v>
       </c>
       <c r="M147" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N147" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O147" t="str">
         <v/>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B148" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C148" t="str">
         <v>Sea Routes</v>
@@ -7349,10 +7349,10 @@
         <v>Yes</v>
       </c>
       <c r="M148" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N148" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O148" t="str">
         <v/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C149" t="str">
         <v>Sea Routes</v>
@@ -7396,10 +7396,10 @@
         <v>Yes</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O149" t="str">
         <v/>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C150" t="str">
         <v>Sea Routes</v>
@@ -7443,10 +7443,10 @@
         <v>Yes</v>
       </c>
       <c r="M150" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N150" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O150" t="str">
         <v/>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B151" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C151" t="str">
         <v>Sea Routes</v>
@@ -7490,10 +7490,10 @@
         <v>Yes</v>
       </c>
       <c r="M151" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N151" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O151" t="str">
         <v/>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B152" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C152" t="str">
         <v>Sea Routes</v>
@@ -7524,8 +7524,8 @@
       <c r="H152" s="1">
         <v>0.025</v>
       </c>
-      <c r="I152" t="str">
-        <v/>
+      <c r="I152" s="1">
+        <v>0.1</v>
       </c>
       <c r="J152" t="str">
         <v>Yes</v>
@@ -7537,10 +7537,10 @@
         <v>Yes</v>
       </c>
       <c r="M152" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N152" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O152" t="str">
         <v/>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B153" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C153" t="str">
         <v>Sea Routes</v>
@@ -7584,10 +7584,10 @@
         <v>Yes</v>
       </c>
       <c r="M153" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N153" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O153" t="str">
         <v/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B154" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C154" t="str">
         <v>Sea Routes</v>
@@ -7618,8 +7618,8 @@
       <c r="H154" s="1">
         <v>0.025</v>
       </c>
-      <c r="I154" t="str">
-        <v/>
+      <c r="I154" s="1">
+        <v>0.1</v>
       </c>
       <c r="J154" t="str">
         <v>Yes</v>
@@ -7631,10 +7631,10 @@
         <v>Yes</v>
       </c>
       <c r="M154" t="str">
-        <v/>
+        <v>Pokemon Mansion</v>
       </c>
       <c r="N154" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":250}}</v>
       </c>
       <c r="O154" t="str">
         <v/>
@@ -7665,8 +7665,8 @@
       <c r="H155" s="1">
         <v>0.2</v>
       </c>
-      <c r="I155" t="str">
-        <v/>
+      <c r="I155" s="1">
+        <v>0.14</v>
       </c>
       <c r="J155" t="str">
         <v>Legacy</v>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C156" t="str">
         <v>Seafoam Islands</v>
@@ -7712,8 +7712,8 @@
       <c r="H156" s="1">
         <v>0.2</v>
       </c>
-      <c r="I156" t="str">
-        <v/>
+      <c r="I156" s="1">
+        <v>0.14</v>
       </c>
       <c r="J156" t="str">
         <v>Legacy</v>
@@ -7725,10 +7725,10 @@
         <v>Yes</v>
       </c>
       <c r="M156" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N156" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O156" t="str">
         <v/>
@@ -7736,10 +7736,10 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B157" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C157" t="str">
         <v>Seafoam Islands</v>
@@ -7772,10 +7772,10 @@
         <v>Yes</v>
       </c>
       <c r="M157" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N157" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O157" t="str">
         <v/>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B158" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C158" t="str">
         <v>Seafoam Islands</v>
@@ -7819,10 +7819,10 @@
         <v>Yes</v>
       </c>
       <c r="M158" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N158" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O158" t="str">
         <v/>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C159" t="str">
         <v>Seafoam Islands</v>
@@ -7866,10 +7866,10 @@
         <v>Yes</v>
       </c>
       <c r="M159" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N159" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O159" t="str">
         <v/>
@@ -7877,10 +7877,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B160" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C160" t="str">
         <v>Seafoam Islands</v>
@@ -7901,7 +7901,7 @@
         <v>0.02</v>
       </c>
       <c r="I160" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J160" t="str">
         <v>Legacy</v>
@@ -7913,10 +7913,10 @@
         <v>Yes</v>
       </c>
       <c r="M160" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N160" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O160" t="str">
         <v/>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="B161" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="C161" t="str">
         <v>Seafoam Islands</v>
@@ -7960,10 +7960,10 @@
         <v>Yes</v>
       </c>
       <c r="M161" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N161" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Articuno","count":5}}</v>
       </c>
       <c r="O161" t="str">
         <v/>
@@ -7994,8 +7994,8 @@
       <c r="H162" s="1">
         <v>0.2</v>
       </c>
-      <c r="I162" t="str">
-        <v/>
+      <c r="I162" s="1">
+        <v>0.14</v>
       </c>
       <c r="J162" t="str">
         <v>Yes</v>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C163" t="str">
         <v>Pokemon Mansion</v>
@@ -8054,10 +8054,10 @@
         <v>Yes</v>
       </c>
       <c r="M163" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N163" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -8065,10 +8065,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C164" t="str">
         <v>Pokemon Mansion</v>
@@ -8088,8 +8088,8 @@
       <c r="H164" s="1">
         <v>0.2</v>
       </c>
-      <c r="I164" t="str">
-        <v/>
+      <c r="I164" s="1">
+        <v>0.14</v>
       </c>
       <c r="J164" t="str">
         <v>Yes</v>
@@ -8101,10 +8101,10 @@
         <v>Yes</v>
       </c>
       <c r="M164" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N164" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C165" t="str">
         <v>Pokemon Mansion</v>
@@ -8148,10 +8148,10 @@
         <v>Yes</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C166" t="str">
         <v>Pokemon Mansion</v>
@@ -8182,8 +8182,8 @@
       <c r="H166" s="1">
         <v>0.2</v>
       </c>
-      <c r="I166" t="str">
-        <v/>
+      <c r="I166" s="1">
+        <v>0.14</v>
       </c>
       <c r="J166" t="str">
         <v>Yes</v>
@@ -8195,10 +8195,10 @@
         <v>Yes</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C167" t="str">
         <v>Pokemon Mansion</v>
@@ -8229,8 +8229,8 @@
       <c r="H167" s="1">
         <v>0.05</v>
       </c>
-      <c r="I167" t="str">
-        <v/>
+      <c r="I167" s="1">
+        <v>0.14</v>
       </c>
       <c r="J167" t="str">
         <v>Yes</v>
@@ -8242,10 +8242,10 @@
         <v>Yes</v>
       </c>
       <c r="M167" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N167" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B168" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C168" t="str">
         <v>Pokemon Mansion</v>
@@ -8276,8 +8276,8 @@
       <c r="H168" s="1">
         <v>0.05</v>
       </c>
-      <c r="I168" t="str">
-        <v/>
+      <c r="I168" s="1">
+        <v>0.16</v>
       </c>
       <c r="J168" t="str">
         <v>Yes</v>
@@ -8289,10 +8289,10 @@
         <v>Yes</v>
       </c>
       <c r="M168" t="str">
-        <v/>
+        <v>Cinnabar Gym</v>
       </c>
       <c r="N168" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magmar","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -8323,8 +8323,8 @@
       <c r="H169" s="1">
         <v>0.2</v>
       </c>
-      <c r="I169" t="str">
-        <v/>
+      <c r="I169" s="1">
+        <v>0.14</v>
       </c>
       <c r="J169" t="str">
         <v>Legacy</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C170" t="str">
         <v>Power Plant</v>
@@ -8370,8 +8370,8 @@
       <c r="H170" s="1">
         <v>0.2</v>
       </c>
-      <c r="I170" t="str">
-        <v/>
+      <c r="I170" s="1">
+        <v>0.14</v>
       </c>
       <c r="J170" t="str">
         <v>Legacy</v>
@@ -8383,10 +8383,10 @@
         <v>Yes</v>
       </c>
       <c r="M170" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N170" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B171" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C171" t="str">
         <v>Power Plant</v>
@@ -8417,8 +8417,8 @@
       <c r="H171" s="1">
         <v>0.2</v>
       </c>
-      <c r="I171" t="str">
-        <v/>
+      <c r="I171" s="1">
+        <v>0.14</v>
       </c>
       <c r="J171" t="str">
         <v>Legacy</v>
@@ -8430,10 +8430,10 @@
         <v>Yes</v>
       </c>
       <c r="M171" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N171" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C172" t="str">
         <v>Power Plant</v>
@@ -8477,10 +8477,10 @@
         <v>Yes</v>
       </c>
       <c r="M172" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -8488,10 +8488,10 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B173" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C173" t="str">
         <v>Power Plant</v>
@@ -8524,10 +8524,10 @@
         <v>Yes</v>
       </c>
       <c r="M173" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N173" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O173" t="str">
         <v/>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B174" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C174" t="str">
         <v>Power Plant</v>
@@ -8558,8 +8558,8 @@
       <c r="H174" s="1">
         <v>0.08</v>
       </c>
-      <c r="I174" t="str">
-        <v/>
+      <c r="I174" s="1">
+        <v>0.14</v>
       </c>
       <c r="J174" t="str">
         <v>Legacy</v>
@@ -8571,10 +8571,10 @@
         <v>Yes</v>
       </c>
       <c r="M174" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N174" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O174" t="str">
         <v/>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B175" t="str">
-        <v/>
+        <v>Extra Challenge A 7</v>
       </c>
       <c r="C175" t="str">
         <v>Power Plant</v>
@@ -8606,7 +8606,7 @@
         <v>0.02</v>
       </c>
       <c r="I175" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.16</v>
       </c>
       <c r="J175" t="str">
         <v>Legacy</v>
@@ -8618,10 +8618,10 @@
         <v>Yes</v>
       </c>
       <c r="M175" t="str">
-        <v/>
+        <v>Seafoam Islands</v>
       </c>
       <c r="N175" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Zapdos","count":5}}</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B177" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C177" t="str">
         <v>Route 22</v>
@@ -8712,10 +8712,10 @@
         <v>Yes</v>
       </c>
       <c r="M177" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N177" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 22","count":350}}</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C178" t="str">
         <v>Route 22</v>
@@ -8759,10 +8759,10 @@
         <v>Yes</v>
       </c>
       <c r="M178" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N178" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 22","count":350}}</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C179" t="str">
         <v>Route 22</v>
@@ -8806,10 +8806,10 @@
         <v>Yes</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 22","count":350}}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C180" t="str">
         <v>Route 22</v>
@@ -8853,10 +8853,10 @@
         <v>Yes</v>
       </c>
       <c r="M180" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N180" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 22","count":350}}</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -8864,10 +8864,10 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B181" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C181" t="str">
         <v>Route 22</v>
@@ -8900,10 +8900,10 @@
         <v>Yes</v>
       </c>
       <c r="M181" t="str">
-        <v/>
+        <v>Route 23</v>
       </c>
       <c r="N181" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 22","count":350}}</v>
       </c>
       <c r="O181" t="str">
         <v/>
@@ -8934,8 +8934,8 @@
       <c r="H182" s="1">
         <v>0.25</v>
       </c>
-      <c r="I182" t="str">
-        <v/>
+      <c r="I182" s="1">
+        <v>0.17</v>
       </c>
       <c r="J182" t="str">
         <v>Yes</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C183" t="str">
         <v>Route 23</v>
@@ -8994,10 +8994,10 @@
         <v>Yes</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Kanto Pokemon League</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Nidoking","Nidoqueen"],"quality":"Rare","count":1}]}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C184" t="str">
         <v>Route 23</v>
@@ -9041,10 +9041,10 @@
         <v>Yes</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Kanto Pokemon League</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Nidoking","Nidoqueen"],"quality":"Rare","count":1}]}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9052,10 +9052,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B185" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C185" t="str">
         <v>Route 23</v>
@@ -9088,10 +9088,10 @@
         <v>Yes</v>
       </c>
       <c r="M185" t="str">
-        <v/>
+        <v>Kanto Pokemon League</v>
       </c>
       <c r="N185" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Nidoking","Nidoqueen"],"quality":"Rare","count":1}]}</v>
       </c>
       <c r="O185" t="str">
         <v/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C186" t="str">
         <v>Route 23</v>
@@ -9135,10 +9135,10 @@
         <v>Yes</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Kanto Pokemon League</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Nidoking","Nidoqueen"],"quality":"Rare","count":1}]}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C187" t="str">
         <v>Route 23</v>
@@ -9182,10 +9182,10 @@
         <v>Yes</v>
       </c>
       <c r="M187" t="str">
-        <v/>
+        <v>Kanto Pokemon League</v>
       </c>
       <c r="N187" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Nidoking","Nidoqueen"],"quality":"Rare","count":1}]}</v>
       </c>
       <c r="O187" t="str">
         <v/>
@@ -9216,8 +9216,8 @@
       <c r="H188" s="1">
         <v>0.25</v>
       </c>
-      <c r="I188" t="str">
-        <v/>
+      <c r="I188" s="1">
+        <v>0.17</v>
       </c>
       <c r="J188" t="str">
         <v>Legacy</v>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B189" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="C189" t="str">
         <v>Victory Road</v>
@@ -9263,8 +9263,8 @@
       <c r="H189" s="1">
         <v>0.25</v>
       </c>
-      <c r="I189" t="str">
-        <v/>
+      <c r="I189" s="1">
+        <v>0.17</v>
       </c>
       <c r="J189" t="str">
         <v>Legacy</v>
@@ -9276,10 +9276,10 @@
         <v>Yes</v>
       </c>
       <c r="M189" t="str">
-        <v/>
+        <v>Cerulean Cave</v>
       </c>
       <c r="N189" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Moltres","count":5}}</v>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -9287,10 +9287,10 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B190" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="C190" t="str">
         <v>Victory Road</v>
@@ -9310,8 +9310,8 @@
       <c r="H190" s="1">
         <v>0.23</v>
       </c>
-      <c r="I190" t="str">
-        <v/>
+      <c r="I190" s="1">
+        <v>0.17</v>
       </c>
       <c r="J190" t="str">
         <v>Legacy</v>
@@ -9323,10 +9323,10 @@
         <v>Yes</v>
       </c>
       <c r="M190" t="str">
-        <v/>
+        <v>Cerulean Cave</v>
       </c>
       <c r="N190" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Moltres","count":5}}</v>
       </c>
       <c r="O190" t="str">
         <v/>
@@ -9334,10 +9334,10 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B191" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="C191" t="str">
         <v>Victory Road</v>
@@ -9370,10 +9370,10 @@
         <v>Yes</v>
       </c>
       <c r="M191" t="str">
-        <v/>
+        <v>Cerulean Cave</v>
       </c>
       <c r="N191" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Moltres","count":5}}</v>
       </c>
       <c r="O191" t="str">
         <v/>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B192" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="C192" t="str">
         <v>Victory Road</v>
@@ -9404,8 +9404,8 @@
       <c r="H192" s="1">
         <v>0.1</v>
       </c>
-      <c r="I192" t="str">
-        <v/>
+      <c r="I192" s="1">
+        <v>0.17</v>
       </c>
       <c r="J192" t="str">
         <v>Legacy</v>
@@ -9417,10 +9417,10 @@
         <v>Yes</v>
       </c>
       <c r="M192" t="str">
-        <v/>
+        <v>Cerulean Cave</v>
       </c>
       <c r="N192" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Moltres","count":5}}</v>
       </c>
       <c r="O192" t="str">
         <v/>
@@ -9428,10 +9428,10 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Extra Challenge A 8</v>
       </c>
       <c r="B193" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="C193" t="str">
         <v>Victory Road</v>
@@ -9452,7 +9452,7 @@
         <v>0.02</v>
       </c>
       <c r="I193" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J193" t="str">
         <v>Legacy</v>
@@ -9464,10 +9464,10 @@
         <v>Yes</v>
       </c>
       <c r="M193" t="str">
-        <v/>
+        <v>Cerulean Cave</v>
       </c>
       <c r="N193" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Moltres","count":5}}</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -9498,8 +9498,8 @@
       <c r="H194" s="1">
         <v>0.2</v>
       </c>
-      <c r="I194" t="str">
-        <v/>
+      <c r="I194" s="1">
+        <v>0.14</v>
       </c>
       <c r="J194" t="str">
         <v>Legacy</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B195" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C195" t="str">
         <v>Cerulean Cave</v>
@@ -9558,10 +9558,10 @@
         <v>Yes</v>
       </c>
       <c r="M195" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N195" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C196" t="str">
         <v>Cerulean Cave</v>
@@ -9605,10 +9605,10 @@
         <v>Yes</v>
       </c>
       <c r="M196" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N196" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C197" t="str">
         <v>Cerulean Cave</v>
@@ -9652,10 +9652,10 @@
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9663,10 +9663,10 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B198" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C198" t="str">
         <v>Cerulean Cave</v>
@@ -9699,10 +9699,10 @@
         <v>Yes</v>
       </c>
       <c r="M198" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N198" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C199" t="str">
         <v>Cerulean Cave</v>
@@ -9746,10 +9746,10 @@
         <v>Yes</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Extra Challenge A 9</v>
       </c>
       <c r="B200" t="str">
-        <v/>
+        <v>Extra Challenge A 10</v>
       </c>
       <c r="C200" t="str">
         <v>Cerulean Cave</v>
@@ -9781,7 +9781,7 @@
         <v>0.01</v>
       </c>
       <c r="I200" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.16</v>
       </c>
       <c r="J200" t="str">
         <v>Legacy</v>
@@ -9793,10 +9793,10 @@
         <v>Yes</v>
       </c>
       <c r="M200" t="str">
-        <v/>
+        <v>Kanto Pokemon League, Key for Indigo Summit</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Mewtwo","count":5}}</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C202" t="str">
         <v>Small Fishing Spot</v>
@@ -9887,10 +9887,10 @@
         <v>Yes</v>
       </c>
       <c r="M202" t="str">
-        <v/>
+        <v>Fighting Dojo, Casino - Eeveelutions</v>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}],"catchEachFromSlotMachine":{"machines":[["Ivysaur","Charmeleon","Wartortle"]]}}</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9898,10 +9898,10 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B203" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C203" t="str">
         <v>Small Fishing Spot</v>
@@ -9934,10 +9934,10 @@
         <v>Yes</v>
       </c>
       <c r="M203" t="str">
-        <v/>
+        <v>Fighting Dojo, Casino - Eeveelutions</v>
       </c>
       <c r="N203" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}],"catchEachFromSlotMachine":{"machines":[["Ivysaur","Charmeleon","Wartortle"]]}}</v>
       </c>
       <c r="O203" t="str">
         <v/>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B204" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C204" t="str">
         <v>Small Fishing Spot</v>
@@ -9981,10 +9981,10 @@
         <v>Yes</v>
       </c>
       <c r="M204" t="str">
-        <v/>
+        <v>Fighting Dojo, Casino - Eeveelutions</v>
       </c>
       <c r="N204" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}],"catchEachFromSlotMachine":{"machines":[["Ivysaur","Charmeleon","Wartortle"]]}}</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B206" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C206" t="str">
         <v>Big Fishing Spot</v>
@@ -10062,8 +10062,8 @@
       <c r="H206" s="1">
         <v>0.05</v>
       </c>
-      <c r="I206" t="str">
-        <v/>
+      <c r="I206" s="1">
+        <v>0.14</v>
       </c>
       <c r="J206" t="str">
         <v/>
@@ -10075,10 +10075,10 @@
         <v>Yes</v>
       </c>
       <c r="M206" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N206" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O206" t="str">
         <v/>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C207" t="str">
         <v>Big Fishing Spot</v>
@@ -10110,7 +10110,7 @@
         <v>0.02</v>
       </c>
       <c r="I207" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J207" t="str">
         <v/>
@@ -10122,10 +10122,10 @@
         <v>Yes</v>
       </c>
       <c r="M207" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N207" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O207" t="str">
         <v/>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C208" t="str">
         <v>Big Fishing Spot</v>
@@ -10157,7 +10157,7 @@
         <v>0.25</v>
       </c>
       <c r="I208" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J208" t="str">
         <v/>
@@ -10169,10 +10169,10 @@
         <v>Yes</v>
       </c>
       <c r="M208" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N208" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O208" t="str">
         <v/>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C209" t="str">
         <v>Big Fishing Spot</v>
@@ -10203,8 +10203,8 @@
       <c r="H209" s="1">
         <v>0.2</v>
       </c>
-      <c r="I209" t="str">
-        <v/>
+      <c r="I209" s="1">
+        <v>0.14</v>
       </c>
       <c r="J209" t="str">
         <v/>
@@ -10216,10 +10216,10 @@
         <v>Yes</v>
       </c>
       <c r="M209" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C210" t="str">
         <v>Big Fishing Spot</v>
@@ -10263,10 +10263,10 @@
         <v>Yes</v>
       </c>
       <c r="M210" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N210" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O210" t="str">
         <v/>
@@ -10274,10 +10274,10 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B211" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C211" t="str">
         <v>Big Fishing Spot</v>
@@ -10310,10 +10310,10 @@
         <v>Yes</v>
       </c>
       <c r="M211" t="str">
-        <v/>
+        <v>Fossil Revival Lab, Casino - Late Troupe</v>
       </c>
       <c r="N211" t="str">
-        <v/>
+        <v>{"catchByQualityAndType":{"type":"Dragon","quality":"Rare","count":2},"catchEachFromSlotMachine":{"machines":[["Lapras","Porygon","Lickitung"]]}}</v>
       </c>
       <c r="O211" t="str">
         <v/>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B213" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C213" t="str">
         <v>Fossil Revival Lab</v>
@@ -10404,10 +10404,10 @@
         <v>Yes</v>
       </c>
       <c r="M213" t="str">
-        <v/>
+        <v>Trade With Friends Hub, Battle Stadium</v>
       </c>
       <c r="N213" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Aerodactyl","quality":"Rare","count":1}],"catchEachFromSlotMachine":{"machines":[["Venusaur","Charizard","Blastoise"]]}}</v>
       </c>
       <c r="O213" t="str">
         <v/>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B214" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C214" t="str">
         <v>Fossil Revival Lab</v>
@@ -10451,10 +10451,10 @@
         <v>Yes</v>
       </c>
       <c r="M214" t="str">
-        <v/>
+        <v>Trade With Friends Hub, Battle Stadium</v>
       </c>
       <c r="N214" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Aerodactyl","quality":"Rare","count":1}],"catchEachFromSlotMachine":{"machines":[["Venusaur","Charizard","Blastoise"]]}}</v>
       </c>
       <c r="O214" t="str">
         <v/>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B215" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C215" t="str">
         <v>Fossil Revival Lab</v>
@@ -10498,10 +10498,10 @@
         <v>Yes</v>
       </c>
       <c r="M215" t="str">
-        <v/>
+        <v>Trade With Friends Hub, Battle Stadium</v>
       </c>
       <c r="N215" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Aerodactyl","quality":"Rare","count":1}],"catchEachFromSlotMachine":{"machines":[["Venusaur","Charizard","Blastoise"]]}}</v>
       </c>
       <c r="O215" t="str">
         <v/>
@@ -10509,10 +10509,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C216" t="str">
         <v>Fossil Revival Lab</v>
@@ -10545,10 +10545,10 @@
         <v>Yes</v>
       </c>
       <c r="M216" t="str">
-        <v/>
+        <v>Trade With Friends Hub, Battle Stadium</v>
       </c>
       <c r="N216" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Aerodactyl","quality":"Rare","count":1}],"catchEachFromSlotMachine":{"machines":[["Venusaur","Charizard","Blastoise"]]}}</v>
       </c>
       <c r="O216" t="str">
         <v/>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B218" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C218" t="str">
         <v>Fighting Dojo</v>
@@ -10639,10 +10639,10 @@
         <v>Yes</v>
       </c>
       <c r="M218" t="str">
-        <v/>
+        <v>Big Fishing Spot, Casino - Special Spot</v>
       </c>
       <c r="N218" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Hitmonchan","quality":"Rare","count":1},{"species":"Hitmonlee","quality":"Rare","count":1},{"species":"Eevee","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O218" t="str">
         <v/>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B219" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C219" t="str">
         <v>Fighting Dojo</v>
@@ -10686,10 +10686,10 @@
         <v>Yes</v>
       </c>
       <c r="M219" t="str">
-        <v/>
+        <v>Big Fishing Spot, Casino - Special Spot</v>
       </c>
       <c r="N219" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Hitmonchan","quality":"Rare","count":1},{"species":"Hitmonlee","quality":"Rare","count":1},{"species":"Eevee","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O219" t="str">
         <v/>
@@ -10697,10 +10697,10 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B220" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C220" t="str">
         <v>Fighting Dojo</v>
@@ -10733,10 +10733,10 @@
         <v>Yes</v>
       </c>
       <c r="M220" t="str">
-        <v/>
+        <v>Big Fishing Spot, Casino - Special Spot</v>
       </c>
       <c r="N220" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Hitmonchan","quality":"Rare","count":1},{"species":"Hitmonlee","quality":"Rare","count":1},{"species":"Eevee","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O220" t="str">
         <v/>
@@ -10791,10 +10791,10 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B222" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C222" t="str">
         <v>Trade With Friends Hub</v>
@@ -10827,10 +10827,10 @@
         <v>Yes</v>
       </c>
       <c r="M222" t="str">
-        <v/>
+        <v>Power Plant</v>
       </c>
       <c r="N222" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gengar","count":1},{"species":"Golem","count":1},{"species":"Alakazam","count":1},{"species":"Machamp","count":1}]}</v>
       </c>
       <c r="O222" t="str">
         <v/>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C223" t="str">
         <v>Trade With Friends Hub</v>
@@ -10874,10 +10874,10 @@
         <v>Yes</v>
       </c>
       <c r="M223" t="str">
-        <v/>
+        <v>Power Plant</v>
       </c>
       <c r="N223" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gengar","count":1},{"species":"Golem","count":1},{"species":"Alakazam","count":1},{"species":"Machamp","count":1}]}</v>
       </c>
       <c r="O223" t="str">
         <v/>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C224" t="str">
         <v>Trade With Friends Hub</v>
@@ -10921,10 +10921,10 @@
         <v>Yes</v>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>Power Plant</v>
       </c>
       <c r="N224" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gengar","count":1},{"species":"Golem","count":1},{"species":"Alakazam","count":1},{"species":"Machamp","count":1}]}</v>
       </c>
       <c r="O224" t="str">
         <v/>
@@ -10979,7 +10979,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Key for Indigo Summit</v>
       </c>
       <c r="B226" t="str">
         <v/>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v/>
+        <v>Key for Indigo Summit</v>
       </c>
       <c r="B227" t="str">
         <v/>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Key for Indigo Summit</v>
       </c>
       <c r="B228" t="str">
         <v/>
@@ -11120,7 +11120,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Key for Indigo Summit</v>
       </c>
       <c r="B229" t="str">
         <v/>
@@ -11165,16 +11165,674 @@
         <v/>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Pewter Gym</v>
+      </c>
+      <c r="D230" t="str">
+        <v/>
+      </c>
+      <c r="E230" t="str">
+        <v/>
+      </c>
+      <c r="F230" t="str">
+        <v/>
+      </c>
+      <c r="G230" t="str">
+        <v/>
+      </c>
+      <c r="H230" t="str">
+        <v/>
+      </c>
+      <c r="I230" t="str">
+        <v/>
+      </c>
+      <c r="J230" t="str">
+        <v/>
+      </c>
+      <c r="K230" t="str">
+        <v/>
+      </c>
+      <c r="L230" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M230" t="str">
+        <v>Route 3</v>
+      </c>
+      <c r="N230" t="str">
+        <v>{"earnBadge":{"name":"Boulder Badge","leader":"Brock","badgeCount":1}}</v>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Cerulean Gym</v>
+      </c>
+      <c r="D231" t="str">
+        <v/>
+      </c>
+      <c r="E231" t="str">
+        <v/>
+      </c>
+      <c r="F231" t="str">
+        <v/>
+      </c>
+      <c r="G231" t="str">
+        <v/>
+      </c>
+      <c r="H231" t="str">
+        <v/>
+      </c>
+      <c r="I231" t="str">
+        <v/>
+      </c>
+      <c r="J231" t="str">
+        <v/>
+      </c>
+      <c r="K231" t="str">
+        <v/>
+      </c>
+      <c r="L231" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M231" t="str">
+        <v>Route 24</v>
+      </c>
+      <c r="N231" t="str">
+        <v>{"earnBadge":{"name":"Cascade Badge","leader":"Misty","badgeCount":2}}</v>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Vermilion Gym</v>
+      </c>
+      <c r="D232" t="str">
+        <v/>
+      </c>
+      <c r="E232" t="str">
+        <v/>
+      </c>
+      <c r="F232" t="str">
+        <v/>
+      </c>
+      <c r="G232" t="str">
+        <v/>
+      </c>
+      <c r="H232" t="str">
+        <v/>
+      </c>
+      <c r="I232" t="str">
+        <v/>
+      </c>
+      <c r="J232" t="str">
+        <v/>
+      </c>
+      <c r="K232" t="str">
+        <v/>
+      </c>
+      <c r="L232" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M232" t="str">
+        <v>Route 11</v>
+      </c>
+      <c r="N232" t="str">
+        <v>{"earnBadge":{"name":"Thunder Badge","leader":"Lt. Surge","badgeCount":3}}</v>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Challenge 19</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Celadon Gym</v>
+      </c>
+      <c r="D233" t="str">
+        <v/>
+      </c>
+      <c r="E233" t="str">
+        <v/>
+      </c>
+      <c r="F233" t="str">
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <v/>
+      </c>
+      <c r="J233" t="str">
+        <v/>
+      </c>
+      <c r="K233" t="str">
+        <v/>
+      </c>
+      <c r="L233" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M233" t="str">
+        <v>Route 7, Casino, Casino - Starter Troupe</v>
+      </c>
+      <c r="N233" t="str">
+        <v>{"earnBadge":{"name":"Rainbow Badge","leader":"Erika","badgeCount":4}}</v>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Route 14,15</v>
+      </c>
+      <c r="D234" t="str">
+        <v/>
+      </c>
+      <c r="E234" t="str">
+        <v/>
+      </c>
+      <c r="F234" t="str">
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <v>No</v>
+      </c>
+      <c r="M234" t="str">
+        <v>Fuchsia Gym</v>
+      </c>
+      <c r="N234" t="str">
+        <v>{"catchSpecies":[{"species":"Ditto","count":5}]}</v>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Fuchsia Gym</v>
+      </c>
+      <c r="D235" t="str">
+        <v/>
+      </c>
+      <c r="E235" t="str">
+        <v/>
+      </c>
+      <c r="F235" t="str">
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <v/>
+      </c>
+      <c r="J235" t="str">
+        <v/>
+      </c>
+      <c r="K235" t="str">
+        <v/>
+      </c>
+      <c r="L235" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M235" t="str">
+        <v>Cycling Road (16-18)</v>
+      </c>
+      <c r="N235" t="str">
+        <v>{"earnBadge":{"name":"Soul Badge","leader":"Koga","badgeCount":5}}</v>
+      </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Cycling Road (16-18)</v>
+      </c>
+      <c r="D236" t="str">
+        <v/>
+      </c>
+      <c r="E236" t="str">
+        <v/>
+      </c>
+      <c r="F236" t="str">
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <v/>
+      </c>
+      <c r="J236" t="str">
+        <v/>
+      </c>
+      <c r="K236" t="str">
+        <v/>
+      </c>
+      <c r="L236" t="str">
+        <v>No</v>
+      </c>
+      <c r="M236" t="str">
+        <v>Safari Zone</v>
+      </c>
+      <c r="N236" t="str">
+        <v>{"catchSpecies":[{"species":"Dodrio","count":2}]}</v>
+      </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Saffron Gym</v>
+      </c>
+      <c r="D237" t="str">
+        <v/>
+      </c>
+      <c r="E237" t="str">
+        <v/>
+      </c>
+      <c r="F237" t="str">
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <v/>
+      </c>
+      <c r="J237" t="str">
+        <v/>
+      </c>
+      <c r="K237" t="str">
+        <v/>
+      </c>
+      <c r="L237" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M237" t="str">
+        <v>Sea Routes</v>
+      </c>
+      <c r="N237" t="str">
+        <v>{"earnBadge":{"name":"Marsh Badge","leader":"Sabrina","badgeCount":6}}</v>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Cinnabar Gym</v>
+      </c>
+      <c r="D238" t="str">
+        <v/>
+      </c>
+      <c r="E238" t="str">
+        <v/>
+      </c>
+      <c r="F238" t="str">
+        <v/>
+      </c>
+      <c r="G238" t="str">
+        <v/>
+      </c>
+      <c r="H238" t="str">
+        <v/>
+      </c>
+      <c r="I238" t="str">
+        <v/>
+      </c>
+      <c r="J238" t="str">
+        <v/>
+      </c>
+      <c r="K238" t="str">
+        <v/>
+      </c>
+      <c r="L238" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M238" t="str">
+        <v>Viridian Gym</v>
+      </c>
+      <c r="N238" t="str">
+        <v>{"earnBadge":{"name":"Volcano Badge","leader":"Blaine","badgeCount":7}}</v>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Viridian Gym</v>
+      </c>
+      <c r="D239" t="str">
+        <v/>
+      </c>
+      <c r="E239" t="str">
+        <v/>
+      </c>
+      <c r="F239" t="str">
+        <v/>
+      </c>
+      <c r="G239" t="str">
+        <v/>
+      </c>
+      <c r="H239" t="str">
+        <v/>
+      </c>
+      <c r="I239" t="str">
+        <v/>
+      </c>
+      <c r="J239" t="str">
+        <v/>
+      </c>
+      <c r="K239" t="str">
+        <v/>
+      </c>
+      <c r="L239" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M239" t="str">
+        <v>Route 22</v>
+      </c>
+      <c r="N239" t="str">
+        <v>{"earnBadge":{"name":"Earth Badge","leader":"Giovanni","badgeCount":8}}</v>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Kanto Pokemon League</v>
+      </c>
+      <c r="D240" t="str">
+        <v/>
+      </c>
+      <c r="E240" t="str">
+        <v/>
+      </c>
+      <c r="F240" t="str">
+        <v/>
+      </c>
+      <c r="G240" t="str">
+        <v/>
+      </c>
+      <c r="H240" t="str">
+        <v/>
+      </c>
+      <c r="I240" t="str">
+        <v/>
+      </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
+      <c r="K240" t="str">
+        <v/>
+      </c>
+      <c r="L240" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M240" t="str">
+        <v>New Region to Travel, Extra Challenge B</v>
+      </c>
+      <c r="N240" t="str">
+        <v>{"defeatEliteFourAndChampion":true}</v>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Casino</v>
+      </c>
+      <c r="D241" t="str">
+        <v/>
+      </c>
+      <c r="E241" t="str">
+        <v/>
+      </c>
+      <c r="F241" t="str">
+        <v/>
+      </c>
+      <c r="G241" t="str">
+        <v/>
+      </c>
+      <c r="H241" t="str">
+        <v/>
+      </c>
+      <c r="I241" t="str">
+        <v/>
+      </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
+      <c r="K241" t="str">
+        <v/>
+      </c>
+      <c r="L241" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M241" t="str">
+        <v>Small Fishing Spot, Casino - Mid Troupe</v>
+      </c>
+      <c r="N241" t="str">
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1}]}</v>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Extra Challenge B</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Extra Challenge B</v>
+      </c>
+      <c r="D242" t="str">
+        <v/>
+      </c>
+      <c r="E242" t="str">
+        <v/>
+      </c>
+      <c r="F242" t="str">
+        <v/>
+      </c>
+      <c r="G242" t="str">
+        <v/>
+      </c>
+      <c r="H242" t="str">
+        <v/>
+      </c>
+      <c r="I242" t="str">
+        <v/>
+      </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
+      <c r="K242" t="str">
+        <v/>
+      </c>
+      <c r="L242" t="str">
+        <v>No</v>
+      </c>
+      <c r="M242" t="str">
+        <v>Key for Indigo Summit</v>
+      </c>
+      <c r="N242" t="str">
+        <v>{"catchSpeciesUniqueCount":150}</v>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Extra Challenge A 10</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Key for Indigo Summit</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Key for Indigo Summit</v>
+      </c>
+      <c r="D243" t="str">
+        <v/>
+      </c>
+      <c r="E243" t="str">
+        <v/>
+      </c>
+      <c r="F243" t="str">
+        <v/>
+      </c>
+      <c r="G243" t="str">
+        <v/>
+      </c>
+      <c r="H243" t="str">
+        <v/>
+      </c>
+      <c r="I243" t="str">
+        <v/>
+      </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
+      <c r="K243" t="str">
+        <v/>
+      </c>
+      <c r="L243" t="str">
+        <v>No</v>
+      </c>
+      <c r="M243" t="str">
+        <v>Indigo Summit</v>
+      </c>
+      <c r="N243" t="str">
+        <v>{"completeChallenges":["Extra Challenge A 10","Extra Challenge B"]}</v>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O229"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O243"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11876,9 +12534,289 @@
         <v/>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B36" t="str">
+        <v>{"earnBadge":{"name":"Boulder Badge","leader":"Brock","badgeCount":1}}</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Route 3</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B37" t="str">
+        <v>{"earnBadge":{"name":"Cascade Badge","leader":"Misty","badgeCount":2}}</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Route 24</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="B38" t="str">
+        <v>{"earnBadge":{"name":"Thunder Badge","leader":"Lt. Surge","badgeCount":3}}</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Route 11</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B39" t="str">
+        <v>{"earnBadge":{"name":"Rainbow Badge","leader":"Erika","badgeCount":4}}</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Route 7, Casino, Casino - Starter Troupe</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B40" t="str">
+        <v>{"catchSpecies":[{"species":"Ditto","count":5}]}</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Fuchsia Gym</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B41" t="str">
+        <v>{"earnBadge":{"name":"Soul Badge","leader":"Koga","badgeCount":5}}</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Cycling Road (16-18)</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B42" t="str">
+        <v>{"catchSpecies":[{"species":"Dodrio","count":2}]}</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Safari Zone</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B43" t="str">
+        <v>{"earnBadge":{"name":"Marsh Badge","leader":"Sabrina","badgeCount":6}}</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Sea Routes</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B44" t="str">
+        <v>{"earnBadge":{"name":"Volcano Badge","leader":"Blaine","badgeCount":7}}</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Viridian Gym</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B45" t="str">
+        <v>{"earnBadge":{"name":"Earth Badge","leader":"Giovanni","badgeCount":8}}</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Route 22</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B46" t="str">
+        <v>{"defeatEliteFourAndChampion":true}</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Win Pokemon League</v>
+      </c>
+      <c r="D46" t="str">
+        <v>New Region to Travel, Extra Challenge B</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B47" t="str">
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1}]}</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Small Fishing Spot, Casino - Mid Troupe</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Extra Challenge B</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{"catchSpeciesUniqueCount":150}</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Key for Indigo Summit</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Key for Indigo Summit</v>
+      </c>
+      <c r="B49" t="str">
+        <v>{"completeChallenges":["Extra Challenge A 10","Extra Challenge B"]}</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Indigo Summit</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F49"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/1_Kanto_Data.xlsx
+++ b/1_Kanto_Data.xlsx
@@ -3524,7 +3524,7 @@
         <v>11-15</v>
       </c>
       <c r="G67" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H67" s="1">
         <v>0.3</v>
@@ -3571,7 +3571,7 @@
         <v>11-15</v>
       </c>
       <c r="G68" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H68" s="1">
         <v>0.3</v>
@@ -3618,7 +3618,7 @@
         <v>11-15</v>
       </c>
       <c r="G69" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H69" s="1">
         <v>0.15</v>
@@ -3665,7 +3665,7 @@
         <v>10-14</v>
       </c>
       <c r="G70" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H70" s="1">
         <v>0.15</v>
@@ -3712,7 +3712,7 @@
         <v>10-14</v>
       </c>
       <c r="G71" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H71" s="1">
         <v>0.1</v>
@@ -4276,7 +4276,7 @@
         <v>18-22</v>
       </c>
       <c r="G83" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H83" s="1">
         <v>0.4</v>
@@ -4323,7 +4323,7 @@
         <v>17-21</v>
       </c>
       <c r="G84" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H84" s="1">
         <v>0.35</v>
@@ -4370,7 +4370,7 @@
         <v>18-22</v>
       </c>
       <c r="G85" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H85" s="1">
         <v>0.15</v>
@@ -4417,7 +4417,7 @@
         <v>18-22</v>
       </c>
       <c r="G86" t="str">
-        <v>15-18</v>
+        <v>16-19</v>
       </c>
       <c r="H86" s="1">
         <v>0.1</v>
@@ -4464,7 +4464,7 @@
         <v>19-24</v>
       </c>
       <c r="G87" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H87" s="1">
         <v>0.3</v>
@@ -4511,7 +4511,7 @@
         <v>18-23</v>
       </c>
       <c r="G88" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H88" s="1">
         <v>0.3</v>
@@ -4558,7 +4558,7 @@
         <v>18-23</v>
       </c>
       <c r="G89" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H89" s="1">
         <v>0.15</v>
@@ -4605,7 +4605,7 @@
         <v>18-23</v>
       </c>
       <c r="G90" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H90" s="1">
         <v>0.15</v>
@@ -4652,7 +4652,7 @@
         <v>19-24</v>
       </c>
       <c r="G91" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H91" s="1">
         <v>0.05</v>
@@ -4699,7 +4699,7 @@
         <v>19-24</v>
       </c>
       <c r="G92" t="str">
-        <v>17-20</v>
+        <v>18-21</v>
       </c>
       <c r="H92" s="1">
         <v>0.05</v>
@@ -5075,7 +5075,7 @@
         <v>23-29</v>
       </c>
       <c r="G100" t="str">
-        <v>22-25</v>
+        <v>23-26</v>
       </c>
       <c r="H100" s="1">
         <v>0.9</v>
@@ -5122,7 +5122,7 @@
         <v>29-33</v>
       </c>
       <c r="G101" t="str">
-        <v>22-25</v>
+        <v>23-26</v>
       </c>
       <c r="H101" s="1">
         <v>0.1</v>
@@ -5169,7 +5169,7 @@
         <v>25-30</v>
       </c>
       <c r="G102" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H102" s="1">
         <v>0.3</v>
@@ -5216,7 +5216,7 @@
         <v>25-30</v>
       </c>
       <c r="G103" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H103" s="1">
         <v>0.3</v>
@@ -5263,7 +5263,7 @@
         <v>26-31</v>
       </c>
       <c r="G104" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H104" s="1">
         <v>0.15</v>
@@ -5310,7 +5310,7 @@
         <v>24-29</v>
       </c>
       <c r="G105" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H105" s="1">
         <v>0.15</v>
@@ -5357,7 +5357,7 @@
         <v>24-29</v>
       </c>
       <c r="G106" t="str">
-        <v>24-27</v>
+        <v>25-28</v>
       </c>
       <c r="H106" s="1">
         <v>0.15</v>
@@ -5404,7 +5404,7 @@
         <v>27-32</v>
       </c>
       <c r="G107" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H107" s="1">
         <v>0.35</v>
@@ -5451,7 +5451,7 @@
         <v>26-31</v>
       </c>
       <c r="G108" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H108" s="1">
         <v>0.3</v>
@@ -5498,7 +5498,7 @@
         <v>26-31</v>
       </c>
       <c r="G109" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H109" s="1">
         <v>0.25</v>
@@ -5545,7 +5545,7 @@
         <v>26-30</v>
       </c>
       <c r="G110" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H110" s="1">
         <v>0.05</v>
@@ -5592,7 +5592,7 @@
         <v>26-30</v>
       </c>
       <c r="G111" t="str">
-        <v>26-29</v>
+        <v>27-30</v>
       </c>
       <c r="H111" s="1">
         <v>0.05</v>
@@ -5639,7 +5639,7 @@
         <v>28-34</v>
       </c>
       <c r="G112" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H112" s="1">
         <v>0.4</v>
@@ -5686,7 +5686,7 @@
         <v>28-33</v>
       </c>
       <c r="G113" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H113" s="1">
         <v>0.25</v>
@@ -5733,7 +5733,7 @@
         <v>29-34</v>
       </c>
       <c r="G114" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H114" s="1">
         <v>0.2</v>
@@ -5780,7 +5780,7 @@
         <v>30-35</v>
       </c>
       <c r="G115" t="str">
-        <v>29-32</v>
+        <v>30-33</v>
       </c>
       <c r="H115" s="1">
         <v>0.15</v>
@@ -5827,7 +5827,7 @@
         <v>32-37</v>
       </c>
       <c r="G116" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H116" s="1">
         <v>0.25</v>
@@ -5874,7 +5874,7 @@
         <v>32-37</v>
       </c>
       <c r="G117" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H117" s="1">
         <v>0.25</v>
@@ -5921,7 +5921,7 @@
         <v>32-37</v>
       </c>
       <c r="G118" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H118" s="1">
         <v>0.2</v>
@@ -5968,7 +5968,7 @@
         <v>31-36</v>
       </c>
       <c r="G119" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H119" s="1">
         <v>0.2</v>
@@ -6015,7 +6015,7 @@
         <v>33-38</v>
       </c>
       <c r="G120" t="str">
-        <v>31-34</v>
+        <v>32-35</v>
       </c>
       <c r="H120" s="1">
         <v>0.1</v>
@@ -6109,7 +6109,7 @@
         <v>34-39</v>
       </c>
       <c r="G122" t="str">
-        <v>33-36</v>
+        <v>34-37</v>
       </c>
       <c r="H122" s="1">
         <v>0.3</v>
@@ -6156,7 +6156,7 @@
         <v>33-38</v>
       </c>
       <c r="G123" t="str">
-        <v>33-36</v>
+        <v>34-37</v>
       </c>
       <c r="H123" s="1">
         <v>0.25</v>
@@ -6203,7 +6203,7 @@
         <v>34-39</v>
       </c>
       <c r="G124" t="str">
-        <v>33-36</v>
+        <v>34-37</v>
       </c>
       <c r="H124" s="1">
         <v>0.175</v>
@@ -6250,7 +6250,7 @@
         <v>34-39</v>
       </c>
       <c r="G125" t="str">
-        <v>33-36</v>
+        <v>34-37</v>
       </c>
       <c r="H125" s="1">
         <v>0.175</v>
@@ -6297,7 +6297,7 @@
         <v>35-40</v>
       </c>
       <c r="G126" t="str">
-        <v>33-36</v>
+        <v>34-37</v>
       </c>
       <c r="H126" s="1">
         <v>0.1</v>
@@ -6344,7 +6344,7 @@
         <v>38-43</v>
       </c>
       <c r="G127" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H127" s="1">
         <v>0.7</v>
@@ -6391,7 +6391,7 @@
         <v>40-45</v>
       </c>
       <c r="G128" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H128" s="1">
         <v>0.15</v>
@@ -6438,7 +6438,7 @@
         <v>38-43</v>
       </c>
       <c r="G129" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H129" s="1">
         <v>0.15</v>
@@ -6485,7 +6485,7 @@
         <v>44-48</v>
       </c>
       <c r="G130" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H130" s="1">
         <v>0.2</v>
@@ -6532,7 +6532,7 @@
         <v>44-48</v>
       </c>
       <c r="G131" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H131" s="1">
         <v>0.2</v>
@@ -6579,7 +6579,7 @@
         <v>48-52</v>
       </c>
       <c r="G132" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6626,7 +6626,7 @@
         <v>44-48</v>
       </c>
       <c r="G133" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H133" s="1">
         <v>0.15</v>
@@ -6673,7 +6673,7 @@
         <v>48-52</v>
       </c>
       <c r="G134" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H134" s="1">
         <v>0.15</v>
@@ -6720,7 +6720,7 @@
         <v>50-55</v>
       </c>
       <c r="G135" t="str">
-        <v>38-41</v>
+        <v>39-42</v>
       </c>
       <c r="H135" s="1">
         <v>0.1</v>
@@ -6767,7 +6767,7 @@
         <v>48-52</v>
       </c>
       <c r="G136" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H136" s="1">
         <v>0.2</v>
@@ -6814,7 +6814,7 @@
         <v>48-52</v>
       </c>
       <c r="G137" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H137" s="1">
         <v>0.2</v>
@@ -6861,7 +6861,7 @@
         <v>50-55</v>
       </c>
       <c r="G138" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H138" s="1">
         <v>0.1</v>
@@ -6908,7 +6908,7 @@
         <v>50-55</v>
       </c>
       <c r="G139" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H139" s="1">
         <v>0.1</v>
@@ -6955,7 +6955,7 @@
         <v>50-55</v>
       </c>
       <c r="G140" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H140" s="1">
         <v>0.1</v>
@@ -7002,7 +7002,7 @@
         <v>53-58</v>
       </c>
       <c r="G141" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7049,7 +7049,7 @@
         <v>50-55</v>
       </c>
       <c r="G142" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H142" s="1">
         <v>0.1</v>
@@ -7096,7 +7096,7 @@
         <v>53-58</v>
       </c>
       <c r="G143" t="str">
-        <v>40-44</v>
+        <v>41-45</v>
       </c>
       <c r="H143" s="1">
         <v>0.1</v>
@@ -7284,7 +7284,7 @@
         <v>60-66</v>
       </c>
       <c r="G147" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H147" s="1">
         <v>0.1</v>
@@ -7331,7 +7331,7 @@
         <v>60-66</v>
       </c>
       <c r="G148" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H148" s="1">
         <v>0.1</v>
@@ -7378,7 +7378,7 @@
         <v>63-70</v>
       </c>
       <c r="G149" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H149" s="1">
         <v>0.15</v>
@@ -7425,7 +7425,7 @@
         <v>62-69</v>
       </c>
       <c r="G150" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H150" s="1">
         <v>0.15</v>
@@ -7472,7 +7472,7 @@
         <v>62-69</v>
       </c>
       <c r="G151" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H151" s="1">
         <v>0.1</v>
@@ -7519,7 +7519,7 @@
         <v>63-70</v>
       </c>
       <c r="G152" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H152" s="1">
         <v>0.1</v>
@@ -7566,7 +7566,7 @@
         <v>62-69</v>
       </c>
       <c r="G153" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H153" s="1">
         <v>0.1</v>
@@ -7613,7 +7613,7 @@
         <v>65-72</v>
       </c>
       <c r="G154" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H154" s="1">
         <v>0.1</v>
@@ -7660,7 +7660,7 @@
         <v>65-72</v>
       </c>
       <c r="G155" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H155" s="1">
         <v>0.05</v>
@@ -7707,7 +7707,7 @@
         <v>65-72</v>
       </c>
       <c r="G156" t="str">
-        <v>42-46</v>
+        <v>43-47</v>
       </c>
       <c r="H156" s="1">
         <v>0.05</v>
@@ -7801,7 +7801,7 @@
         <v>68-75</v>
       </c>
       <c r="G158" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H158" s="1">
         <v>0.3</v>
@@ -7848,7 +7848,7 @@
         <v>71-78</v>
       </c>
       <c r="G159" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H159" s="1">
         <v>0.1</v>
@@ -7895,7 +7895,7 @@
         <v>68-75</v>
       </c>
       <c r="G160" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H160" s="1">
         <v>0.15</v>
@@ -7942,7 +7942,7 @@
         <v>71-78</v>
       </c>
       <c r="G161" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H161" s="1">
         <v>0.1</v>
@@ -7989,7 +7989,7 @@
         <v>68-75</v>
       </c>
       <c r="G162" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H162" s="1">
         <v>0.05</v>
@@ -8036,7 +8036,7 @@
         <v>71-78</v>
       </c>
       <c r="G163" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H163" s="1">
         <v>0.05</v>
@@ -8083,7 +8083,7 @@
         <v>68-75</v>
       </c>
       <c r="G164" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8130,7 +8130,7 @@
         <v>71-78</v>
       </c>
       <c r="G165" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H165" s="1">
         <v>0.025</v>
@@ -8177,7 +8177,7 @@
         <v>68-75</v>
       </c>
       <c r="G166" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H166" s="1">
         <v>0.1</v>
@@ -8224,7 +8224,7 @@
         <v>71-78</v>
       </c>
       <c r="G167" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H167" s="1">
         <v>0.025</v>
@@ -8271,7 +8271,7 @@
         <v>72-79</v>
       </c>
       <c r="G168" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H168" s="1">
         <v>0.2</v>
@@ -8318,7 +8318,7 @@
         <v>72-79</v>
       </c>
       <c r="G169" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H169" s="1">
         <v>0.15</v>
@@ -8365,7 +8365,7 @@
         <v>75-82</v>
       </c>
       <c r="G170" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H170" s="1">
         <v>0.2</v>
@@ -8412,7 +8412,7 @@
         <v>75-82</v>
       </c>
       <c r="G171" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H171" s="1">
         <v>0.15</v>
@@ -8459,7 +8459,7 @@
         <v>75-82</v>
       </c>
       <c r="G172" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H172" s="1">
         <v>0.2</v>
@@ -8506,7 +8506,7 @@
         <v>77-84</v>
       </c>
       <c r="G173" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H173" s="1">
         <v>0.05</v>
@@ -8553,7 +8553,7 @@
         <v>77-84</v>
       </c>
       <c r="G174" t="str">
-        <v>47-51</v>
+        <v>48-52</v>
       </c>
       <c r="H174" s="1">
         <v>0.05</v>
@@ -8694,7 +8694,7 @@
         <v>81-88</v>
       </c>
       <c r="G177" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H177" s="1">
         <v>0.15</v>
@@ -8741,7 +8741,7 @@
         <v>79-86</v>
       </c>
       <c r="G178" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H178" s="1">
         <v>0.15</v>
@@ -8788,7 +8788,7 @@
         <v>77-84</v>
       </c>
       <c r="G179" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H179" s="1">
         <v>0.2</v>
@@ -8835,7 +8835,7 @@
         <v>77-84</v>
       </c>
       <c r="G180" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H180" s="1">
         <v>0.2</v>
@@ -8882,7 +8882,7 @@
         <v>79-86</v>
       </c>
       <c r="G181" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H181" s="1">
         <v>0.15</v>
@@ -8929,7 +8929,7 @@
         <v>79-86</v>
       </c>
       <c r="G182" t="str">
-        <v>49-53</v>
+        <v>50-55</v>
       </c>
       <c r="H182" s="1">
         <v>0.15</v>
@@ -8976,7 +8976,7 @@
         <v>83-91</v>
       </c>
       <c r="G183" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H183" s="1">
         <v>0.25</v>
@@ -9023,7 +9023,7 @@
         <v>83-91</v>
       </c>
       <c r="G184" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H184" s="1">
         <v>0.125</v>
@@ -9070,7 +9070,7 @@
         <v>83-91</v>
       </c>
       <c r="G185" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H185" s="1">
         <v>0.125</v>
@@ -9117,7 +9117,7 @@
         <v>83-91</v>
       </c>
       <c r="G186" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H186" s="1">
         <v>0.2</v>
@@ -9164,7 +9164,7 @@
         <v>87-95</v>
       </c>
       <c r="G187" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H187" s="1">
         <v>0.15</v>
@@ -9211,7 +9211,7 @@
         <v>87-95</v>
       </c>
       <c r="G188" t="str">
-        <v>51-56</v>
+        <v>53-58</v>
       </c>
       <c r="H188" s="1">
         <v>0.15</v>
